--- a/基本設計/02_権限基本設計書.xlsx
+++ b/基本設計/02_権限基本設計書.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R8eeb2c024d764ab4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R8486edc9b72b463f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_ロール定義" sheetId="10" r:id="R75fe1fda10484750"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_メニュー権限" sheetId="11" r:id="R5cfb90433d204c65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_機能権限" sheetId="12" r:id="R3da840660aba41bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_権限コード" sheetId="13" r:id="Rbe5034556e694ae3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_API権限対応" sheetId="14" r:id="Rdaacd327ff9a4f3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rb79a9b6b99d34479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Re7154ca3e65e4af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_ロール定義" sheetId="10" r:id="R3c7fb038fa924285"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_メニュー権限" sheetId="11" r:id="Rf0c8a8692af14fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_機能権限" sheetId="12" r:id="Re82370d5d8d645a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_権限コード" sheetId="13" r:id="R1cfd3a207c1c44e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_API権限対応" sheetId="14" r:id="R279f23720aa247d3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1281,10 +1281,7 @@
       <x:c r="F16" s="191"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.8 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
+      <x:c r="A17"/>
       <x:c r="C17"/>
       <x:c r="D17"/>
       <x:c r="E17"/>
@@ -1300,25 +1297,22 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" s="234" t="str">
-        <x:v>本書は Company WorkHub の基本設計内容を定義する。
-Ver.1.7 は状態変更入口、API/DB制約、取込Transaction、日報一意制約、通知・Token保持を整合した再Review対応版である。</x:v>
-      </x:c>
-      <x:c r="C19" s="234"/>
-      <x:c r="D19" s="234"/>
-      <x:c r="E19" s="234"/>
-      <x:c r="F19" s="234"/>
-      <x:c r="G19" s="234"/>
-      <x:c r="H19" s="234"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" s="234"/>
-      <x:c r="C20" s="234"/>
-      <x:c r="D20" s="234"/>
-      <x:c r="E20" s="234"/>
-      <x:c r="F20" s="234"/>
-      <x:c r="G20" s="234"/>
-      <x:c r="H20" s="234"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="234"/>

--- a/基本設計/02_権限基本設計書.xlsx
+++ b/基本設計/02_権限基本設計書.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rb79a9b6b99d34479"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Re7154ca3e65e4af6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_ロール定義" sheetId="10" r:id="R3c7fb038fa924285"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_メニュー権限" sheetId="11" r:id="Rf0c8a8692af14fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_機能権限" sheetId="12" r:id="Re82370d5d8d645a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_権限コード" sheetId="13" r:id="R1cfd3a207c1c44e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_API権限対応" sheetId="14" r:id="R279f23720aa247d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R51d1f6bed6674a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rb903e54b68224279"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_ロール定義" sheetId="10" r:id="Rd120777407f94afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_メニュー権限" sheetId="11" r:id="R704dfdf16c73452a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_機能権限" sheetId="12" r:id="Rc5d3d8f041de4ce0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_権限コード" sheetId="13" r:id="R5072afd4190048ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_API権限対応" sheetId="14" r:id="R58d5e3ab94234d99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_DataScope定義" sheetId="15" r:id="R6d6d49eeaeb9461f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -161,8 +162,19 @@
       <x:color rgb="FF1F1F1F"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF18283A"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FF193C61"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="29">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -304,8 +316,18 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF234F77"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F5FA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -363,11 +385,25 @@
         <x:color rgb="FFA6A6A6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD4DEE8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="235">
+  <x:cellXfs count="254">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -851,6 +887,59 @@
     <x:xf numFmtId="0" fontId="24" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="30" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1149,7 +1238,36 @@
     <x:col min="26" max="26" width="3" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1"/>
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+    </x:row>
     <x:row r="3">
+      <x:c r="A3"/>
       <x:c r="B3" s="221" t="str">
         <x:v>Company WorkHub
 企業従業員・タスク管理システム</x:v>
@@ -1160,8 +1278,13 @@
       <x:c r="F3" s="221"/>
       <x:c r="G3" s="221"/>
       <x:c r="H3" s="221"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4"/>
       <x:c r="B4" s="221"/>
       <x:c r="C4" s="221"/>
       <x:c r="D4" s="221"/>
@@ -1169,8 +1292,13 @@
       <x:c r="F4" s="221"/>
       <x:c r="G4" s="221"/>
       <x:c r="H4" s="221"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5"/>
       <x:c r="B5" s="221"/>
       <x:c r="C5" s="221"/>
       <x:c r="D5" s="221"/>
@@ -1178,8 +1306,13 @@
       <x:c r="F5" s="221"/>
       <x:c r="G5" s="221"/>
       <x:c r="H5" s="221"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6"/>
       <x:c r="B6"/>
       <x:c r="C6"/>
       <x:c r="D6"/>
@@ -1187,8 +1320,27 @@
       <x:c r="F6"/>
       <x:c r="G6"/>
       <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7"/>
+      <x:c r="B7"/>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
+      <x:c r="A8"/>
       <x:c r="B8" s="227" t="str">
         <x:v>権限基本設計書</x:v>
       </x:c>
@@ -1198,8 +1350,13 @@
       <x:c r="F8" s="227"/>
       <x:c r="G8" s="227"/>
       <x:c r="H8" s="227"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
+      <x:c r="A9"/>
       <x:c r="B9" s="227"/>
       <x:c r="C9" s="227"/>
       <x:c r="D9" s="227"/>
@@ -1207,8 +1364,13 @@
       <x:c r="F9" s="227"/>
       <x:c r="G9" s="227"/>
       <x:c r="H9" s="227"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
+      <x:c r="A10"/>
       <x:c r="B10" s="227"/>
       <x:c r="C10" s="227"/>
       <x:c r="D10" s="227"/>
@@ -1216,49 +1378,84 @@
       <x:c r="F10" s="227"/>
       <x:c r="G10" s="227"/>
       <x:c r="H10" s="227"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
+      <x:c r="A11"/>
       <x:c r="B11"/>
-      <x:c r="C11" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C11" s="235" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
       <x:c r="F11"/>
       <x:c r="G11"/>
       <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" s="229" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12" s="237" t="str">
+        <x:v>Document ID</x:v>
       </x:c>
       <x:c r="D12" s="191" t="str">
         <x:v>CW-BD-AUTHZ</x:v>
       </x:c>
       <x:c r="E12" s="191"/>
       <x:c r="F12" s="191"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
       <x:c r="C13" s="229" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="D13" s="191" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="D13" s="238" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="E13" s="191"/>
       <x:c r="F13" s="191"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
       <x:c r="C14" s="229" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="D14" s="191" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="D14" s="238" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E14" s="191"/>
       <x:c r="F14" s="191"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
       <x:c r="C15" s="229" t="str">
         <x:v>作成者</x:v>
       </x:c>
@@ -1267,6 +1464,12 @@
       </x:c>
       <x:c r="E15" s="191"/>
       <x:c r="F15" s="191"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
@@ -1274,24 +1477,35 @@
       <x:c r="C16" s="229" t="str">
         <x:v>状態</x:v>
       </x:c>
-      <x:c r="D16" s="191" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="D16" s="238" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="E16" s="191"/>
       <x:c r="F16" s="191"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="C17"/>
-      <x:c r="D17"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="240"/>
+      <x:c r="B17" s="240"/>
+      <x:c r="C17" s="240"/>
+      <x:c r="D17" s="240"/>
       <x:c r="E17"/>
       <x:c r="F17"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
-      <x:c r="D18"/>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="240"/>
+      <x:c r="B18" s="240"/>
+      <x:c r="C18" s="240" t="str">
+        <x:v>Baseline ID</x:v>
+      </x:c>
+      <x:c r="D18" s="240" t="str">
+        <x:v>BL-2026-09-24</x:v>
+      </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>
     </x:row>
@@ -1388,6 +1602,10 @@
       <x:c r="F1" s="172"/>
       <x:c r="G1" s="172"/>
       <x:c r="H1" s="172"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="172"/>
@@ -1398,42 +1616,42 @@
       <x:c r="F2" s="172"/>
       <x:c r="G2" s="172"/>
       <x:c r="H2" s="172"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="174" t="str">
-        <x:v>システム名</x:v>
-      </x:c>
-      <x:c r="B3" s="139" t="str">
-        <x:v>Company WorkHub</x:v>
-      </x:c>
-      <x:c r="C3" s="139"/>
-      <x:c r="D3" s="174" t="str">
-        <x:v>文書番号</x:v>
-      </x:c>
-      <x:c r="E3" s="139" t="str">
-        <x:v>DOCUMENT-REVISION</x:v>
-      </x:c>
-      <x:c r="F3" s="139"/>
-      <x:c r="G3" s="139"/>
-      <x:c r="H3" s="139"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="174" t="str">
-        <x:v>版数</x:v>
-      </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
-      </x:c>
-      <x:c r="C4" s="139"/>
-      <x:c r="D4" s="174" t="str">
-        <x:v>改訂日</x:v>
-      </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
-      </x:c>
-      <x:c r="F4" s="139"/>
-      <x:c r="G4" s="139"/>
-      <x:c r="H4" s="139"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="244" t="str">
+        <x:v>システム名：Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="63"/>
+      <x:c r="C3" s="63"/>
+      <x:c r="D3" s="244"/>
+      <x:c r="E3" s="63"/>
+      <x:c r="F3" s="63"/>
+      <x:c r="G3" s="63"/>
+      <x:c r="H3" s="63"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="244" t="str">
+        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+      </x:c>
+      <x:c r="B4" s="63"/>
+      <x:c r="C4" s="63"/>
+      <x:c r="D4" s="244"/>
+      <x:c r="E4" s="63"/>
+      <x:c r="F4" s="63"/>
+      <x:c r="G4" s="63"/>
+      <x:c r="H4" s="63"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
@@ -1444,6 +1662,10 @@
       <x:c r="F5"/>
       <x:c r="G5"/>
       <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="175" t="str">
@@ -1456,6 +1678,10 @@
       <x:c r="F6" s="175"/>
       <x:c r="G6" s="175"/>
       <x:c r="H6" s="175"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="181" t="str">
@@ -1465,7 +1691,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="C7" s="181" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>改訂内容</x:v>
       </x:c>
       <x:c r="D7" s="181" t="str">
         <x:v>作成者</x:v>
@@ -1482,6 +1708,10 @@
       <x:c r="H7" s="181" t="str">
         <x:v>備考</x:v>
       </x:c>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="67" t="str">
@@ -1503,11 +1733,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G8" s="67" t="str">
-        <x:v>作成済</x:v>
+        <x:v>作成中</x:v>
       </x:c>
       <x:c r="H8" s="67" t="str">
         <x:v>基本設計初版</x:v>
       </x:c>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="67" t="str">
@@ -1529,11 +1763,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H9" s="67" t="str">
         <x:v>Leader Review後Baseline化</x:v>
       </x:c>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="67" t="str">
@@ -1555,11 +1793,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G10" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H10" s="67" t="str">
         <x:v>Review指摘対応</x:v>
       </x:c>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="67" t="str">
@@ -1581,11 +1823,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G11" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H11" s="67" t="str">
         <x:v>再監査指摘対応</x:v>
       </x:c>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="67" t="str">
@@ -1607,11 +1853,15 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G12" s="67" t="str">
-        <x:v>レビュー待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" s="67" t="str">
         <x:v>再監査第2回指摘対応</x:v>
       </x:c>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
@@ -1632,12 +1882,16 @@
       <x:c r="F13" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G13" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G13" s="235" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>再監査残項対応</x:v>
       </x:c>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -1658,12 +1912,16 @@
       <x:c r="F14" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G14" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G14" s="235" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>再Review指摘対応</x:v>
       </x:c>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
@@ -1684,25 +1942,187 @@
       <x:c r="F15" t="str">
         <x:v>-</x:v>
       </x:c>
-      <x:c r="G15" t="str">
-        <x:v>レビュー待ち</x:v>
+      <x:c r="G15" s="235" t="str">
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>最大10回の反復監査対応</x:v>
+      </x:c>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>2026-08-17</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>通知未読件数APIの利用元を共通Headerへ統一</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G16" s="235" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>04再Review影響反映</x:v>
+      </x:c>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>従業員・部門業務Review：PM参照範囲と操作権限を明確化</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G17" s="235" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>第1回業務仕様Review指摘対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>従業員・部門業務仕様Review：権限範囲・取込単位・用語を整合</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G18" s="235" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>第2回業務仕様Review指摘対応</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="110" customHeight="1">
+      <x:c r="A19" s="236" t="str">
+        <x:v>Ver.2.3</x:v>
+      </x:c>
+      <x:c r="B19" s="236" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C19" s="236" t="str">
+        <x:v>内容・関連Reviewの既確定仕様を整合。業務未決事項は承認待ちとして管理。</x:v>
+      </x:c>
+      <x:c r="D19" s="236" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E19" s="236" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F19" s="236" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G19" s="236" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H19" s="236" t="str">
+        <x:v>2026-09-18指摘対応。正式承認を示すものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="40" customHeight="1">
+      <x:c r="A20" s="236" t="str">
+        <x:v>Ver.2.4</x:v>
+      </x:c>
+      <x:c r="B20" s="236" t="str">
+        <x:v>2026-09-18</x:v>
+      </x:c>
+      <x:c r="C20" s="236" t="str">
+        <x:v>待確認12項目の方針選定、業務/API/DB/画面/運用を連動修正。章立て維持。</x:v>
+      </x:c>
+      <x:c r="D20" s="236" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="E20" s="236" t="str">
+        <x:v>未実施</x:v>
+      </x:c>
+      <x:c r="F20" s="236" t="str">
+        <x:v>未承認</x:v>
+      </x:c>
+      <x:c r="G20" s="236" t="str">
+        <x:v>Review中</x:v>
+      </x:c>
+      <x:c r="H20" s="236" t="str">
+        <x:v>一般社内管理Systemの範囲。旧版はBackup保管。</x:v>
+      </x:c>
+      <x:c r="I20" s="236"/>
+      <x:c r="J20" s="236"/>
+      <x:c r="K20" s="236"/>
+      <x:c r="L20" s="236"/>
+    </x:row>
+    <x:row r="21" ht="100" customHeight="1">
+      <x:c r="A21" s="240" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B21" s="240" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="C21" s="240" t="str">
+        <x:v>共通規則・正本参照・構成・文書管理を統合修正。Baseline承認前の最終整合修正。</x:v>
+      </x:c>
+      <x:c r="D21" s="240" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="E21" s="240" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="F21" s="240" t="str">
+        <x:v>-</x:v>
+      </x:c>
+      <x:c r="G21" s="240" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H21" s="240" t="str">
+        <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:B3"/>
-    <x:mergeCell ref="C3:D3"/>
-    <x:mergeCell ref="E3:F3"/>
-    <x:mergeCell ref="G3:H3"/>
-    <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="G4:H4"/>
     <x:mergeCell ref="A6:H6"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1731,6 +2151,11 @@
       <x:c r="E1" s="20"/>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="20"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="20"/>
@@ -1740,6 +2165,11 @@
       <x:c r="E2" s="20"/>
       <x:c r="F2" s="20"/>
       <x:c r="G2" s="20"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="23" t="str">
@@ -1750,30 +2180,54 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="E3" s="241" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="F3" s="23"/>
       <x:c r="G3" s="21" t="str">
         <x:v>CW-BD-030</x:v>
       </x:c>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="23" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C4" s="242" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="23" t="str">
         <x:v>作成日</x:v>
       </x:c>
       <x:c r="F4" s="23"/>
-      <x:c r="G4" s="24" t="n">
-        <x:v>46239</x:v>
-      </x:c>
+      <x:c r="G4" s="243" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5"/>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="26" t="str">
@@ -1785,6 +2239,11 @@
       <x:c r="E6" s="26"/>
       <x:c r="F6" s="26"/>
       <x:c r="G6" s="26"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="31" t="str">
@@ -1808,6 +2267,11 @@
       <x:c r="G7" s="31" t="str">
         <x:v>備考</x:v>
       </x:c>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="33" t="str">
@@ -1831,6 +2295,11 @@
       <x:c r="G8" s="33" t="str">
         <x:v>最高権限</x:v>
       </x:c>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="33" t="str">
@@ -1846,12 +2315,17 @@
         <x:v>担当PJ変更、Member管理、Task作成/割当/完了承認、Member日報閲覧</x:v>
       </x:c>
       <x:c r="E9" s="33" t="str">
-        <x:v>自分が担当するPJ</x:v>
+        <x:v>ログインUserがPMである未完了PJ（PLANNING/IN_PROGRESS/SUSPENDED）のACTIVE Memberかつ在籍社員。本人を含む。社員詳細内のPJ/Taskは当該PM担当未完了PJ内のみ</x:v>
       </x:c>
       <x:c r="F9" s="33" t="str">
-        <x:v>非担当PJの更新、全社員管理、権限管理不可</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="str"/>
+        <x:v>範囲外社員の参照、社員登録・更新・退職、Excel入出力、部門管理不可</x:v>
+      </x:c>
+      <x:c r="G9" s="33"/>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="33" t="str">
@@ -1872,7 +2346,138 @@
       <x:c r="F10" s="33" t="str">
         <x:v>他人Task更新、直接完了、他人日報閲覧不可</x:v>
       </x:c>
-      <x:c r="G10" s="33" t="str"/>
+      <x:c r="G10" s="33"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+    </x:row>
+    <x:row r="11" ht="54" customHeight="1">
+      <x:c r="A11" s="236" t="str">
+        <x:v>複数Role</x:v>
+      </x:c>
+      <x:c r="B11" s="236" t="str">
+        <x:v>合成規則</x:v>
+      </x:c>
+      <x:c r="C11" s="236" t="str">
+        <x:v>全Userに内蔵Roleを1つ以上必須</x:v>
+      </x:c>
+      <x:c r="D11" s="236" t="str">
+        <x:v>有効RoleのPermissionを和集合。ADMIN専用管理（社員/部門/User/Role/監査）はROLE-ADMIN必須。</x:v>
+      </x:c>
+      <x:c r="E11" s="236" t="str">
+        <x:v>内蔵Roleによる各機能のData範囲の和集合。カスタムRoleは範囲を持たない。</x:v>
+      </x:c>
+      <x:c r="F11" s="236" t="str">
+        <x:v>Permissionがあっても対象Data範囲・本人/担当/承認条件を満たさない操作は禁止。</x:v>
+      </x:c>
+      <x:c r="G11" s="236" t="str">
+        <x:v>11のRole列は標準付与。13のPermissionとData範囲を両方確認。</x:v>
+      </x:c>
+      <x:c r="H11" s="236"/>
+      <x:c r="I11" s="236"/>
+      <x:c r="J11" s="236"/>
+      <x:c r="K11" s="236"/>
+      <x:c r="L11" s="236"/>
+    </x:row>
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="236" t="str">
+        <x:v>組込Role保護</x:v>
+      </x:c>
+      <x:c r="B12" s="236" t="str">
+        <x:v>ROLE-ADMIN/ROLE-PM/ROLE-EMP</x:v>
+      </x:c>
+      <x:c r="C12" s="236" t="str">
+        <x:v>初期登録の固定Role</x:v>
+      </x:c>
+      <x:c r="D12" s="236" t="str">
+        <x:v>名称/説明のみ変更可。Code/Permission/状態は固定。</x:v>
+      </x:c>
+      <x:c r="E12" s="236" t="str">
+        <x:v>全User</x:v>
+      </x:c>
+      <x:c r="F12" s="236" t="str">
+        <x:v>停止/削除/Permission変更禁止。自身ADMIN剥奪・自身停止禁止、最後の有効ADMIN保護。</x:v>
+      </x:c>
+      <x:c r="G12" s="236" t="str">
+        <x:v>既存画面で保護項目非活性、APIでもCOMMON-4000。</x:v>
+      </x:c>
+      <x:c r="H12" s="236"/>
+      <x:c r="I12" s="236"/>
+      <x:c r="J12" s="236"/>
+      <x:c r="K12" s="236"/>
+      <x:c r="L12" s="236"/>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" s="236" t="str">
+        <x:v>カスタムRole</x:v>
+      </x:c>
+      <x:c r="B13" s="236" t="str">
+        <x:v>独自Role</x:v>
+      </x:c>
+      <x:c r="C13" s="236" t="str">
+        <x:v>追加Permissionの設定</x:v>
+      </x:c>
+      <x:c r="D13" s="236" t="str">
+        <x:v>ACTIVEで新規。Codeは登録後変更不可。停止は割当Userが0件（停止User含む）のみ。再開可。</x:v>
+      </x:c>
+      <x:c r="E13" s="236" t="str">
+        <x:v>範囲は内蔵Roleの定義を継承</x:v>
+      </x:c>
+      <x:c r="F13" s="236" t="str">
+        <x:v>使用中停止・停止Roleの新規割当不可。</x:v>
+      </x:c>
+      <x:c r="G13" s="236" t="str">
+        <x:v>PM任命資格/ADMIN専用操作はカスタムCodeでは代替不可。</x:v>
+      </x:c>
+      <x:c r="H13" s="236"/>
+      <x:c r="I13" s="236"/>
+      <x:c r="J13" s="236"/>
+      <x:c r="K13" s="236"/>
+      <x:c r="L13" s="236"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1910,6 +2515,12 @@
       <x:c r="D1" s="20"/>
       <x:c r="E1" s="20"/>
       <x:c r="F1" s="20"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="20"/>
@@ -1918,6 +2529,12 @@
       <x:c r="D2" s="20"/>
       <x:c r="E2" s="20"/>
       <x:c r="F2" s="20"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="23" t="str">
@@ -1928,30 +2545,50 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="E3" s="241" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="F3" s="23"/>
-      <x:c r="G3" t="str">
-        <x:v>CW-BD-031</x:v>
-      </x:c>
+      <x:c r="G3" t="str"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="23" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C4" s="242" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
-      <x:c r="E4" s="23" t="str">
-        <x:v>作成日</x:v>
+      <x:c r="E4" s="241" t="str">
+        <x:v>作成日：2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="35"/>
-      <x:c r="G4" s="36" t="n">
-        <x:v>46239</x:v>
-      </x:c>
+      <x:c r="G4" s="36"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5"/>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="26" t="str">
@@ -1962,6 +2599,12 @@
       <x:c r="D6" s="26"/>
       <x:c r="E6" s="26"/>
       <x:c r="F6" s="26"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="31" t="str">
@@ -1982,6 +2625,12 @@
       <x:c r="F7" s="31" t="str">
         <x:v>表示条件・備考</x:v>
       </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="33" t="str">
@@ -2002,6 +2651,12 @@
       <x:c r="F8" s="33" t="str">
         <x:v>統計範囲を権限で制御</x:v>
       </x:c>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="33" t="str">
@@ -2020,8 +2675,14 @@
         <x:v>×</x:v>
       </x:c>
       <x:c r="F9" s="33" t="str">
-        <x:v>PMは関係社員参照のみ</x:v>
-      </x:c>
+        <x:v>PMは担当する未完了PJのACTIVE Memberかつ在籍社員のみ参照。更新系Menu/操作は非表示</x:v>
+      </x:c>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="33" t="str">
@@ -2039,7 +2700,13 @@
       <x:c r="E10" s="33" t="str">
         <x:v>×</x:v>
       </x:c>
-      <x:c r="F10" s="33" t="str"/>
+      <x:c r="F10" s="33"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="33" t="str">
@@ -2060,6 +2727,12 @@
       <x:c r="F11" s="33" t="str">
         <x:v>担当・参加範囲</x:v>
       </x:c>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="33" t="str">
@@ -2077,7 +2750,15 @@
       <x:c r="E12" s="33" t="str">
         <x:v>○</x:v>
       </x:c>
-      <x:c r="F12" s="33" t="str"/>
+      <x:c r="F12" s="33" t="str">
+        <x:v>SCR-008をmine=trueで表示。新規画面ではない。</x:v>
+      </x:c>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="33" t="str">
@@ -2098,6 +2779,12 @@
       <x:c r="F13" s="33" t="str">
         <x:v>PMは担当PJ</x:v>
       </x:c>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="33" t="str">
@@ -2115,7 +2802,13 @@
       <x:c r="E14" s="33" t="str">
         <x:v>○</x:v>
       </x:c>
-      <x:c r="F14" s="33" t="str"/>
+      <x:c r="F14" s="33"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="33" t="str">
@@ -2136,6 +2829,12 @@
       <x:c r="F15" s="33" t="str">
         <x:v>参加PJのみ</x:v>
       </x:c>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="33" t="str">
@@ -2153,7 +2852,13 @@
       <x:c r="E16" s="33" t="str">
         <x:v>○</x:v>
       </x:c>
-      <x:c r="F16" s="33" t="str"/>
+      <x:c r="F16" s="33"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="33" t="str">
@@ -2175,7 +2880,7 @@
         <x:v>PMは担当PJ</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="40" customHeight="1">
       <x:c r="A18" s="33" t="str">
         <x:v>日報管理</x:v>
       </x:c>
@@ -2183,15 +2888,23 @@
         <x:v>日報統計</x:v>
       </x:c>
       <x:c r="C18" s="33" t="str">
-        <x:v>○</x:v>
+        <x:v>×</x:v>
       </x:c>
       <x:c r="D18" s="33" t="str">
-        <x:v>○</x:v>
+        <x:v>×</x:v>
       </x:c>
       <x:c r="E18" s="33" t="str">
         <x:v>×</x:v>
       </x:c>
-      <x:c r="F18" s="33" t="str"/>
+      <x:c r="F18" s="33" t="str">
+        <x:v>第1期非提供（Menu非表示）。Dashboard既存集計を利用。</x:v>
+      </x:c>
+      <x:c r="G18" s="236"/>
+      <x:c r="H18" s="236"/>
+      <x:c r="I18" s="236"/>
+      <x:c r="J18" s="236"/>
+      <x:c r="K18" s="236"/>
+      <x:c r="L18" s="236"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="33" t="str">
@@ -2276,9 +2989,8 @@
     <x:mergeCell ref="F3:G3"/>
     <x:mergeCell ref="A4:B4"/>
     <x:mergeCell ref="C4:D4"/>
-    <x:mergeCell ref="E4:F4"/>
-    <x:mergeCell ref="F4:G4"/>
     <x:mergeCell ref="A6:F6"/>
+    <x:mergeCell ref="E4:G4"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2307,6 +3019,11 @@
       <x:c r="E1" s="20"/>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="20"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="20"/>
@@ -2316,6 +3033,11 @@
       <x:c r="E2" s="20"/>
       <x:c r="F2" s="20"/>
       <x:c r="G2" s="20"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="23" t="str">
@@ -2326,30 +3048,54 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="D3" s="21"/>
-      <x:c r="E3" s="23" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="E3" s="241" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="F3" s="23"/>
       <x:c r="G3" s="21" t="str">
         <x:v>CW-BD-032</x:v>
       </x:c>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="23" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="23"/>
-      <x:c r="C4" s="21" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="C4" s="242" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="23" t="str">
         <x:v>作成日</x:v>
       </x:c>
       <x:c r="F4" s="23"/>
-      <x:c r="G4" s="24" t="n">
-        <x:v>46239</x:v>
-      </x:c>
+      <x:c r="G4" s="243" t="str">
+        <x:v>2026-09-24</x:v>
+      </x:c>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5"/>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="26" t="str">
@@ -2361,6 +3107,11 @@
       <x:c r="E6" s="26"/>
       <x:c r="F6" s="26"/>
       <x:c r="G6" s="26"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="31" t="str">
@@ -2384,6 +3135,11 @@
       <x:c r="G7" s="31" t="str">
         <x:v>バックエンド制御</x:v>
       </x:c>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="33" t="str">
@@ -2407,6 +3163,11 @@
       <x:c r="G8" s="33" t="str">
         <x:v>必須</x:v>
       </x:c>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="33" t="str">
@@ -2422,18 +3183,23 @@
         <x:v>×</x:v>
       </x:c>
       <x:c r="E9" s="33" t="str">
-        <x:v>PMは関係者のみ</x:v>
+        <x:v>ADMIN=全社員。PM=担当未完了PJのACTIVE Memberかつ在籍社員。範囲外ID直接指定は権限Error</x:v>
       </x:c>
       <x:c r="F9" s="33" t="str">
-        <x:v>ボタン/メニュー制御</x:v>
+        <x:v>新規/編集/退職/Import/Exportを権限別制御</x:v>
       </x:c>
       <x:c r="G9" s="33" t="str">
         <x:v>必須</x:v>
       </x:c>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="33" t="str">
-        <x:v>社員登録/更新/停止</x:v>
+        <x:v>社員登録/更新/退職</x:v>
       </x:c>
       <x:c r="B10" s="33" t="str">
         <x:v>○</x:v>
@@ -2445,14 +3211,19 @@
         <x:v>×</x:v>
       </x:c>
       <x:c r="E10" s="33" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>管理者のみ。一般情報更新と退職処理を分離</x:v>
       </x:c>
       <x:c r="F10" s="33" t="str">
-        <x:v>ボタン/メニュー制御</x:v>
+        <x:v>PMは更新系Buttonを非表示</x:v>
       </x:c>
       <x:c r="G10" s="33" t="str">
         <x:v>必須</x:v>
       </x:c>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="33" t="str">
@@ -2467,13 +3238,18 @@
       <x:c r="D11" s="33" t="str">
         <x:v>×</x:v>
       </x:c>
-      <x:c r="E11" s="33" t="str"/>
+      <x:c r="E11" s="33"/>
       <x:c r="F11" s="33" t="str">
         <x:v>ボタン/メニュー制御</x:v>
       </x:c>
       <x:c r="G11" s="33" t="str">
         <x:v>必須</x:v>
       </x:c>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="33" t="str">
@@ -2488,13 +3264,18 @@
       <x:c r="D12" s="33" t="str">
         <x:v>×</x:v>
       </x:c>
-      <x:c r="E12" s="33" t="str"/>
+      <x:c r="E12" s="33"/>
       <x:c r="F12" s="33" t="str">
         <x:v>ボタン/メニュー制御</x:v>
       </x:c>
       <x:c r="G12" s="33" t="str">
         <x:v>必須</x:v>
       </x:c>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="33" t="str">
@@ -2518,6 +3299,11 @@
       <x:c r="G13" s="33" t="str">
         <x:v>必須</x:v>
       </x:c>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="33" t="str">
@@ -2532,13 +3318,18 @@
       <x:c r="D14" s="33" t="str">
         <x:v>×</x:v>
       </x:c>
-      <x:c r="E14" s="33" t="str"/>
+      <x:c r="E14" s="33"/>
       <x:c r="F14" s="33" t="str">
         <x:v>ボタン/メニュー制御</x:v>
       </x:c>
       <x:c r="G14" s="33" t="str">
         <x:v>必須</x:v>
       </x:c>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="33" t="str">
@@ -2553,13 +3344,18 @@
       <x:c r="D15" s="33" t="str">
         <x:v>×</x:v>
       </x:c>
-      <x:c r="E15" s="33" t="str"/>
+      <x:c r="E15" s="33"/>
       <x:c r="F15" s="33" t="str">
         <x:v>ボタン/メニュー制御</x:v>
       </x:c>
       <x:c r="G15" s="33" t="str">
         <x:v>必須</x:v>
       </x:c>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="33" t="str">
@@ -2583,6 +3379,11 @@
       <x:c r="G16" s="33" t="str">
         <x:v>必須</x:v>
       </x:c>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="33" t="str">
@@ -2751,7 +3552,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="E24" s="33" t="str">
-        <x:v>同日一件</x:v>
+        <x:v>同一社員・同一PJ・同一日一件</x:v>
       </x:c>
       <x:c r="F24" s="33" t="str">
         <x:v>ボタン/メニュー制御</x:v>
@@ -2859,6 +3660,12 @@
       <x:c r="D1" s="68"/>
       <x:c r="E1" s="68"/>
       <x:c r="F1" s="68"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="68"/>
@@ -2867,6 +3674,12 @@
       <x:c r="D2" s="68"/>
       <x:c r="E2" s="68"/>
       <x:c r="F2" s="68"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="62" t="str">
@@ -2875,30 +3688,42 @@
       <x:c r="B3" s="63" t="str">
         <x:v>Company WorkHub</x:v>
       </x:c>
-      <x:c r="C3" s="62" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="C3" s="244" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="D3" s="63" t="str">
         <x:v>CW-BD-033</x:v>
       </x:c>
       <x:c r="E3" s="63"/>
       <x:c r="F3" s="63"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="62" t="str">
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.1.8</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="62" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D4" s="63" t="str">
-        <x:v>2026-08-12</x:v>
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="E4" s="63"/>
       <x:c r="F4" s="63"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="64"/>
@@ -2907,6 +3732,12 @@
       <x:c r="D5" s="64"/>
       <x:c r="E5" s="64"/>
       <x:c r="F5" s="64"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="65" t="str">
@@ -2917,6 +3748,12 @@
       <x:c r="D6" s="65"/>
       <x:c r="E6" s="65"/>
       <x:c r="F6" s="65"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="66" t="str">
@@ -2937,6 +3774,12 @@
       <x:c r="F7" s="66" t="str">
         <x:v>Data範囲</x:v>
       </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="67" t="str">
@@ -2957,6 +3800,12 @@
       <x:c r="F8" s="67" t="str">
         <x:v>Role別Data範囲</x:v>
       </x:c>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="67" t="str">
@@ -2975,15 +3824,21 @@
         <x:v>ADMIN/PM</x:v>
       </x:c>
       <x:c r="F9" s="67" t="str">
-        <x:v>PMは担当PJ関係社員</x:v>
-      </x:c>
+        <x:v>ADMIN=全社員。PM=担当未完了PJのACTIVE Memberかつ在籍社員（本人含む）</x:v>
+      </x:c>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="67" t="str">
         <x:v>PERM-EMP-WRITE</x:v>
       </x:c>
       <x:c r="B10" s="67" t="str">
-        <x:v>社員登録更新停止</x:v>
+        <x:v>社員登録更新退職</x:v>
       </x:c>
       <x:c r="C10" s="67" t="str">
         <x:v>M03</x:v>
@@ -2995,8 +3850,14 @@
         <x:v>ADMIN</x:v>
       </x:c>
       <x:c r="F10" s="67" t="str">
-        <x:v>全社</x:v>
-      </x:c>
+        <x:v>全社。社員登録・一般情報更新・退職・Excel入出力</x:v>
+      </x:c>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="67" t="str">
@@ -3015,8 +3876,14 @@
         <x:v>ADMIN</x:v>
       </x:c>
       <x:c r="F11" s="67" t="str">
-        <x:v>全社</x:v>
-      </x:c>
+        <x:v>全社。部門登録・更新・停止・削除</x:v>
+      </x:c>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="67" t="str">
@@ -3037,6 +3904,12 @@
       <x:c r="F12" s="67" t="str">
         <x:v>担当・参加PJ</x:v>
       </x:c>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="67" t="str">
@@ -3057,6 +3930,12 @@
       <x:c r="F13" s="67" t="str">
         <x:v>PMは担当PJ</x:v>
       </x:c>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="67" t="str">
@@ -3077,6 +3956,12 @@
       <x:c r="F14" s="67" t="str">
         <x:v>PMは担当PJ</x:v>
       </x:c>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="67" t="str">
@@ -3097,6 +3982,12 @@
       <x:c r="F15" s="67" t="str">
         <x:v>権限範囲</x:v>
       </x:c>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="67" t="str">
@@ -3117,6 +4008,12 @@
       <x:c r="F16" s="67" t="str">
         <x:v>PMは担当PJ</x:v>
       </x:c>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="67" t="str">
@@ -3337,6 +4234,11 @@
       <x:c r="E1" s="138"/>
       <x:c r="F1" s="138"/>
       <x:c r="G1" s="138"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="138"/>
@@ -3346,6 +4248,11 @@
       <x:c r="E2" s="138"/>
       <x:c r="F2" s="138"/>
       <x:c r="G2" s="138"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="141" t="str">
@@ -3355,31 +4262,55 @@
         <x:v>Company WorkHub</x:v>
       </x:c>
       <x:c r="C3" s="139"/>
-      <x:c r="D3" s="141" t="str">
-        <x:v>文書番号</x:v>
+      <x:c r="D3" s="244" t="str">
+        <x:v>章ID</x:v>
       </x:c>
       <x:c r="E3" s="139" t="str">
         <x:v>CW-BD-023</x:v>
       </x:c>
       <x:c r="F3" s="139"/>
       <x:c r="G3" s="139"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="141" t="str">
         <x:v>版数</x:v>
       </x:c>
-      <x:c r="B4" s="139" t="str">
-        <x:v>Ver.1.8</x:v>
+      <x:c r="B4" s="63" t="str">
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="141" t="str">
         <x:v>改訂日</x:v>
       </x:c>
-      <x:c r="E4" s="139" t="str">
-        <x:v>2026-08-12</x:v>
+      <x:c r="E4" s="63" t="str">
+        <x:v>2026-09-24</x:v>
       </x:c>
       <x:c r="F4" s="139"/>
       <x:c r="G4" s="139"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5"/>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="142" t="str">
@@ -3391,6 +4322,11 @@
       <x:c r="E6" s="142"/>
       <x:c r="F6" s="142"/>
       <x:c r="G6" s="142"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="147" t="str">
@@ -3414,6 +4350,11 @@
       <x:c r="G7" s="147" t="str">
         <x:v>画面／利用元</x:v>
       </x:c>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="151" t="str">
@@ -3429,7 +4370,7 @@
         <x:v>不要</x:v>
       </x:c>
       <x:c r="E8" s="151" t="str">
-        <x:v>未認証</x:v>
+        <x:v>DS-AUTH-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F8" s="151" t="str">
         <x:v>認証済/本人/共通条件</x:v>
@@ -3437,6 +4378,11 @@
       <x:c r="G8" s="151" t="str">
         <x:v>SCR-001</x:v>
       </x:c>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="151" t="str">
@@ -3452,7 +4398,7 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E9" s="151" t="str">
-        <x:v>本人Tokenのみ</x:v>
+        <x:v>DS-AUTH-002（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F9" s="151" t="str">
         <x:v>認証済/本人/共通条件</x:v>
@@ -3460,6 +4406,11 @@
       <x:c r="G9" s="151" t="str">
         <x:v>共通Header</x:v>
       </x:c>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="151" t="str">
@@ -3475,7 +4426,7 @@
         <x:v>Refresh Cookie</x:v>
       </x:c>
       <x:c r="E10" s="151" t="str">
-        <x:v>有効・未失効Token</x:v>
+        <x:v>DS-AUTH-003（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F10" s="151" t="str">
         <x:v>認証済/本人/共通条件</x:v>
@@ -3483,6 +4434,11 @@
       <x:c r="G10" s="151" t="str">
         <x:v>共通Interceptor</x:v>
       </x:c>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="151" t="str">
@@ -3498,7 +4454,7 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E11" s="151" t="str">
-        <x:v>本人</x:v>
+        <x:v>DS-AUTH-004（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F11" s="151" t="str">
         <x:v>認証済/本人/共通条件</x:v>
@@ -3506,6 +4462,11 @@
       <x:c r="G11" s="151" t="str">
         <x:v>共通Layout</x:v>
       </x:c>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="151" t="str">
@@ -3521,7 +4482,7 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E12" s="151" t="str">
-        <x:v>本人</x:v>
+        <x:v>DS-AUTH-005（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F12" s="151" t="str">
         <x:v>認証済/本人/共通条件</x:v>
@@ -3529,6 +4490,11 @@
       <x:c r="G12" s="151" t="str">
         <x:v>SCR-026</x:v>
       </x:c>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="151" t="str">
@@ -3544,7 +4510,7 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E13" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人・参加PJ</x:v>
+        <x:v>DS-DASH-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F13" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3552,6 +4518,11 @@
       <x:c r="G13" s="151" t="str">
         <x:v>SCR-002</x:v>
       </x:c>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="151" t="str">
@@ -3567,7 +4538,7 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E14" s="151" t="str">
-        <x:v>一般=有効部門, 管理者=指定可</x:v>
+        <x:v>DS-DEPT-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F14" s="151" t="str">
         <x:v>認証済/本人/共通条件</x:v>
@@ -3575,6 +4546,11 @@
       <x:c r="G14" s="151" t="str">
         <x:v>SCR-007</x:v>
       </x:c>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="151" t="str">
@@ -3590,7 +4566,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E15" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-DEPT-002（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F15" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3598,6 +4574,11 @@
       <x:c r="G15" s="151" t="str">
         <x:v>SCR-007</x:v>
       </x:c>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="151" t="str">
@@ -3613,7 +4594,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E16" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-DEPT-003（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F16" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3621,6 +4602,11 @@
       <x:c r="G16" s="151" t="str">
         <x:v>SCR-007</x:v>
       </x:c>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="151" t="str">
@@ -3636,7 +4622,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E17" s="151" t="str">
-        <x:v>自己・子孫を親に設定不可</x:v>
+        <x:v>DS-DEPT-004（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F17" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3659,7 +4645,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E18" s="151" t="str">
-        <x:v>社員・子部門・PJ関連なし</x:v>
+        <x:v>DS-DEPT-005（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F18" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3682,7 +4668,7 @@
         <x:v>管理者/PM</x:v>
       </x:c>
       <x:c r="E19" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ関係社員</x:v>
+        <x:v>DS-EMP-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F19" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3705,7 +4691,7 @@
         <x:v>管理者/PM</x:v>
       </x:c>
       <x:c r="E20" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ関係社員</x:v>
+        <x:v>DS-EMP-002（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F20" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3728,7 +4714,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E21" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-EMP-003（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F21" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3751,7 +4737,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E22" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-EMP-004（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F22" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3774,13 +4760,13 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E23" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-EMP-005（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F23" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
       </x:c>
       <x:c r="G23" s="151" t="str">
-        <x:v>SCR-005, SCR-006</x:v>
+        <x:v>SCR-005</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3797,7 +4783,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E24" s="151" t="str">
-        <x:v>管理者のみ; 全件検証後一括Commit</x:v>
+        <x:v>DS-EMP-006（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F24" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3820,7 +4806,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E25" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-EMP-007（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F25" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3843,7 +4829,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E26" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-LOG-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F26" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3866,7 +4852,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E27" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-LOG-002（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F27" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3889,7 +4875,7 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E28" s="151" t="str">
-        <x:v>有効部門</x:v>
+        <x:v>DS-MST-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F28" s="151" t="str">
         <x:v>認証済/本人/共通条件</x:v>
@@ -3898,7 +4884,7 @@
         <x:v>SCR-003, SCR-004, SCR-007, SCR-021</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
+    <x:row r="29" ht="96" customHeight="1">
       <x:c r="A29" s="151" t="str">
         <x:v>API-MST-002</x:v>
       </x:c>
@@ -3906,20 +4892,25 @@
         <x:v>社員選択肢</x:v>
       </x:c>
       <x:c r="C29" s="151" t="str">
-        <x:v>PERM-EMP-READ</x:v>
+        <x:v>DEFAULT:PERM-EMP-READ / PROJECT_PM:PERM-PRJ-WRITE / PROJECT_MEMBER:PERM-MEMBER-WRITE / TASK_ASSIGNEE:PERM-TASK-WRITE</x:v>
       </x:c>
       <x:c r="D29" s="151" t="str">
         <x:v>管理者/PM</x:v>
       </x:c>
       <x:c r="E29" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ候補</x:v>
+        <x:v>DS-MST-002（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F29" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
       </x:c>
       <x:c r="G29" s="151" t="str">
-        <x:v>SCR-007, SCR-009, SCR-012, SCR-013, SCR-015, SCR-021</x:v>
-      </x:c>
+        <x:v>既存利用画面、およびSCR-009/010:PROJECT_PM、SCR-012:PROJECT_MEMBER、SCR-015/016:TASK_ASSIGNEE</x:v>
+      </x:c>
+      <x:c r="H29" s="236"/>
+      <x:c r="I29" s="236"/>
+      <x:c r="J29" s="236"/>
+      <x:c r="K29" s="236"/>
+      <x:c r="L29" s="236"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="151" t="str">
@@ -3935,7 +4926,7 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E30" s="151" t="str">
-        <x:v>権限範囲内PJ</x:v>
+        <x:v>DS-MST-003（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F30" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3958,7 +4949,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E31" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-MST-004（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F31" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -3981,7 +4972,7 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E32" s="151" t="str">
-        <x:v>本人通知のみ</x:v>
+        <x:v>DS-NTF-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F32" s="151" t="str">
         <x:v>認証済/本人/共通条件</x:v>
@@ -4004,13 +4995,13 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E33" s="151" t="str">
-        <x:v>本人通知のみ</x:v>
+        <x:v>DS-NTF-002（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F33" s="151" t="str">
         <x:v>認証済/本人/共通条件</x:v>
       </x:c>
       <x:c r="G33" s="151" t="str">
-        <x:v>共通Header/SCR-002</x:v>
+        <x:v>共通Header</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -4027,7 +5018,7 @@
         <x:v>本人</x:v>
       </x:c>
       <x:c r="E34" s="151" t="str">
-        <x:v>受信者本人</x:v>
+        <x:v>DS-NTF-003（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F34" s="151" t="str">
         <x:v>認証済/本人/共通条件</x:v>
@@ -4050,7 +5041,7 @@
         <x:v>本人</x:v>
       </x:c>
       <x:c r="E35" s="151" t="str">
-        <x:v>受信者本人</x:v>
+        <x:v>DS-NTF-004（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F35" s="151" t="str">
         <x:v>認証済/本人/共通条件</x:v>
@@ -4073,7 +5064,7 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E36" s="151" t="str">
-        <x:v>ADMIN=全社, PM/EMP=担当・参加PJ</x:v>
+        <x:v>DS-PRJ-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F36" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4096,7 +5087,7 @@
         <x:v>関係者</x:v>
       </x:c>
       <x:c r="E37" s="151" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
+        <x:v>DS-PRJ-002（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F37" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4119,7 +5110,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E38" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-PRJ-003（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F38" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4142,7 +5133,7 @@
         <x:v>管理者/担当PM</x:v>
       </x:c>
       <x:c r="E39" s="151" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
+        <x:v>DS-PRJ-004（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F39" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4151,7 +5142,7 @@
         <x:v>SCR-010</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
+    <x:row r="40" ht="40" customHeight="1">
       <x:c r="A40" s="151" t="str">
         <x:v>API-PRJ-005</x:v>
       </x:c>
@@ -4165,7 +5156,7 @@
         <x:v>管理者/担当PM</x:v>
       </x:c>
       <x:c r="E40" s="151" t="str">
-        <x:v>完了時に未完了Taskなし</x:v>
+        <x:v>DS-PRJ-005（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F40" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4173,6 +5164,11 @@
       <x:c r="G40" s="151" t="str">
         <x:v>SCR-010, SCR-011</x:v>
       </x:c>
+      <x:c r="H40" s="236"/>
+      <x:c r="I40" s="236"/>
+      <x:c r="J40" s="236"/>
+      <x:c r="K40" s="236"/>
+      <x:c r="L40" s="236"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="151" t="str">
@@ -4188,7 +5184,7 @@
         <x:v>関係者</x:v>
       </x:c>
       <x:c r="E41" s="151" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
+        <x:v>DS-PRJ-006（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F41" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4211,7 +5207,7 @@
         <x:v>管理者/担当PM</x:v>
       </x:c>
       <x:c r="E42" s="151" t="str">
-        <x:v>ADMINまたは当該PJのPM; 在籍社員</x:v>
+        <x:v>DS-PRJ-007（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F42" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4234,7 +5230,7 @@
         <x:v>管理者/担当PM</x:v>
       </x:c>
       <x:c r="E43" s="151" t="str">
-        <x:v>PM・未完了Task担当者は削除不可</x:v>
+        <x:v>DS-PRJ-008（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F43" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4257,7 +5253,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E44" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-ROLE-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F44" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4280,7 +5276,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E45" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-ROLE-002（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F45" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4303,7 +5299,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E46" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-ROLE-003（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F46" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4326,7 +5322,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E47" s="151" t="str">
-        <x:v>組込Role Code変更禁止</x:v>
+        <x:v>DS-ROLE-004（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F47" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4349,7 +5345,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E48" s="151" t="str">
-        <x:v>使用中Role停止時確認</x:v>
+        <x:v>DS-ROLE-005（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F48" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4372,7 +5368,7 @@
         <x:v>権限別</x:v>
       </x:c>
       <x:c r="E49" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人</x:v>
+        <x:v>DS-RPT-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F49" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4395,7 +5391,7 @@
         <x:v>権限別</x:v>
       </x:c>
       <x:c r="E50" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人</x:v>
+        <x:v>DS-RPT-002（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F50" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4404,7 +5400,7 @@
         <x:v>SCR-019, SCR-020, SCR-021</x:v>
       </x:c>
     </x:row>
-    <x:row r="51">
+    <x:row r="51" ht="40" customHeight="1">
       <x:c r="A51" s="151" t="str">
         <x:v>API-RPT-003</x:v>
       </x:c>
@@ -4418,7 +5414,7 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E51" s="151" t="str">
-        <x:v>本人; 当該PJ Member</x:v>
+        <x:v>DS-RPT-003（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F51" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4426,6 +5422,11 @@
       <x:c r="G51" s="151" t="str">
         <x:v>SCR-020</x:v>
       </x:c>
+      <x:c r="H51" s="236"/>
+      <x:c r="I51" s="236"/>
+      <x:c r="J51" s="236"/>
+      <x:c r="K51" s="236"/>
+      <x:c r="L51" s="236"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="151" t="str">
@@ -4441,7 +5442,7 @@
         <x:v>本人/管理者</x:v>
       </x:c>
       <x:c r="E52" s="151" t="str">
-        <x:v>本人=当日・前営業日, ADMIN=全期間</x:v>
+        <x:v>DS-RPT-004（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F52" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4464,7 +5465,7 @@
         <x:v>本人/管理者</x:v>
       </x:c>
       <x:c r="E53" s="151" t="str">
-        <x:v>本人=当日・前営業日, ADMIN=全期間</x:v>
+        <x:v>DS-RPT-005（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F53" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4487,7 +5488,7 @@
         <x:v>管理者/担当PM</x:v>
       </x:c>
       <x:c r="E54" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ</x:v>
+        <x:v>DS-RPT-006（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F54" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4510,7 +5511,7 @@
         <x:v>全員</x:v>
       </x:c>
       <x:c r="E55" s="151" t="str">
-        <x:v>ADMIN=全社, PM=担当PJ, EMP=参加PJ・本人Task</x:v>
+        <x:v>DS-TASK-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F55" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4533,7 +5534,7 @@
         <x:v>関係者</x:v>
       </x:c>
       <x:c r="E56" s="151" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
+        <x:v>DS-TASK-002（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F56" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4556,7 +5557,7 @@
         <x:v>管理者/担当PM</x:v>
       </x:c>
       <x:c r="E57" s="151" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
+        <x:v>DS-TASK-003（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F57" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4579,7 +5580,7 @@
         <x:v>管理者/担当PM</x:v>
       </x:c>
       <x:c r="E58" s="151" t="str">
-        <x:v>ADMINまたは当該PJのPM</x:v>
+        <x:v>DS-TASK-004（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F58" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4588,7 +5589,7 @@
         <x:v>SCR-016</x:v>
       </x:c>
     </x:row>
-    <x:row r="59">
+    <x:row r="59" ht="91" customHeight="1">
       <x:c r="A59" s="151" t="str">
         <x:v>API-TASK-005</x:v>
       </x:c>
@@ -4602,10 +5603,10 @@
         <x:v>権限別</x:v>
       </x:c>
       <x:c r="E59" s="151" t="str">
-        <x:v>担当者=TODO/進行/REVIEW; PM/ADMIN=承認・差戻し・取消</x:v>
+        <x:v>DS-TASK-005（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F59" s="151" t="str">
-        <x:v>Permission + Data範囲</x:v>
+        <x:v>着手・未着手へ戻す・確認依頼：PERM-TASK-PROGRESS、かつ担当者/担当PM/ADMIN。承認・差戻し：PERM-TASK-APPROVE、かつ担当PM/ADMIN。取消：PERM-TASK-WRITE、かつ担当PM/ADMIN。16／27の合法遷移も満たすこと。</x:v>
       </x:c>
       <x:c r="G59" s="151" t="str">
         <x:v>SCR-017, SCR-018</x:v>
@@ -4625,7 +5626,7 @@
         <x:v>担当者/PM/管理者</x:v>
       </x:c>
       <x:c r="E60" s="151" t="str">
-        <x:v>担当者または担当PM/ADMIN</x:v>
+        <x:v>DS-TASK-006（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F60" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4642,13 +5643,13 @@
         <x:v>Comment登録</x:v>
       </x:c>
       <x:c r="C61" s="151" t="str">
-        <x:v>PERM-TASK-READ（PJ Member）</x:v>
+        <x:v>PERM-TASK-READ</x:v>
       </x:c>
       <x:c r="D61" s="151" t="str">
         <x:v>PJ Member</x:v>
       </x:c>
       <x:c r="E61" s="151" t="str">
-        <x:v>当該PJ Member</x:v>
+        <x:v>DS-TASK-007（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F61" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4671,7 +5672,7 @@
         <x:v>関係者</x:v>
       </x:c>
       <x:c r="E62" s="151" t="str">
-        <x:v>ADMINまたはPJ Member</x:v>
+        <x:v>DS-TASK-008（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F62" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4694,7 +5695,7 @@
         <x:v>関係者</x:v>
       </x:c>
       <x:c r="E63" s="151" t="str">
-        <x:v>ADMIN/PM/PJ Member</x:v>
+        <x:v>DS-TASK-009（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F63" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4717,7 +5718,7 @@
         <x:v>関係者</x:v>
       </x:c>
       <x:c r="E64" s="151" t="str">
-        <x:v>ADMIN/PM/PJ Member</x:v>
+        <x:v>DS-TASK-010（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F64" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4740,7 +5741,7 @@
         <x:v>権限者</x:v>
       </x:c>
       <x:c r="E65" s="151" t="str">
-        <x:v>ADMIN/担当PM/Upload者</x:v>
+        <x:v>DS-TASK-011（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F65" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4763,7 +5764,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E66" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-USR-001（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F66" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4786,7 +5787,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E67" s="151" t="str">
-        <x:v>管理者のみ</x:v>
+        <x:v>DS-USR-002（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F67" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4809,7 +5810,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E68" s="151" t="str">
-        <x:v>管理者のみ; 自身のADMIN剥奪禁止</x:v>
+        <x:v>DS-USR-003（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F68" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4832,7 +5833,7 @@
         <x:v>管理者</x:v>
       </x:c>
       <x:c r="E69" s="151" t="str">
-        <x:v>管理者のみ; 有効User</x:v>
+        <x:v>DS-USR-004（14_DataScope定義参照）</x:v>
       </x:c>
       <x:c r="F69" s="151" t="str">
         <x:v>Permission + Data範囲</x:v>
@@ -4869,4 +5870,1144 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="248" t="str">
+        <x:v>14_DataScope定義</x:v>
+      </x:c>
+      <x:c r="B1" s="247"/>
+      <x:c r="C1" s="247"/>
+      <x:c r="D1" s="247"/>
+      <x:c r="E1" s="247"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="247"/>
+      <x:c r="B2" s="247"/>
+      <x:c r="C2" s="247"/>
+      <x:c r="D2" s="247"/>
+      <x:c r="E2" s="247"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="247" t="str">
+        <x:v>Company WorkHub</x:v>
+      </x:c>
+      <x:c r="B3" s="247"/>
+      <x:c r="C3" s="247"/>
+      <x:c r="D3" s="247"/>
+      <x:c r="E3" s="247"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="247"/>
+      <x:c r="B4" s="247"/>
+      <x:c r="C4" s="247"/>
+      <x:c r="D4" s="247"/>
+      <x:c r="E4" s="247"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="247" t="str">
+        <x:v>BL-2026-09-24 / Review中</x:v>
+      </x:c>
+      <x:c r="B5" s="247"/>
+      <x:c r="C5" s="247"/>
+      <x:c r="D5" s="247"/>
+      <x:c r="E5" s="247"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="247"/>
+      <x:c r="B6" s="247"/>
+      <x:c r="C6" s="247"/>
+      <x:c r="D6" s="247"/>
+      <x:c r="E6" s="247"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
+      <x:c r="A7" s="250" t="str">
+        <x:v>Data Scope ID</x:v>
+      </x:c>
+      <x:c r="B7" s="250" t="str">
+        <x:v>対象API</x:v>
+      </x:c>
+      <x:c r="C7" s="250" t="str">
+        <x:v>Role</x:v>
+      </x:c>
+      <x:c r="D7" s="250" t="str">
+        <x:v>対象範囲・操作条件</x:v>
+      </x:c>
+      <x:c r="E7" s="250" t="str">
+        <x:v>判定条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="252" t="str">
+        <x:v>DS-AUTH-001</x:v>
+      </x:c>
+      <x:c r="B8" s="252" t="str">
+        <x:v>API-AUTH-001</x:v>
+      </x:c>
+      <x:c r="C8" s="252" t="str">
+        <x:v>不要</x:v>
+      </x:c>
+      <x:c r="D8" s="252" t="str">
+        <x:v>未認証</x:v>
+      </x:c>
+      <x:c r="E8" s="252" t="str">
+        <x:v>認証済/本人/共通条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="251" t="str">
+        <x:v>DS-AUTH-002</x:v>
+      </x:c>
+      <x:c r="B9" s="251" t="str">
+        <x:v>API-AUTH-002</x:v>
+      </x:c>
+      <x:c r="C9" s="251" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D9" s="251" t="str">
+        <x:v>本人Tokenのみ</x:v>
+      </x:c>
+      <x:c r="E9" s="251" t="str">
+        <x:v>認証済/本人/共通条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="252" t="str">
+        <x:v>DS-AUTH-003</x:v>
+      </x:c>
+      <x:c r="B10" s="252" t="str">
+        <x:v>API-AUTH-003</x:v>
+      </x:c>
+      <x:c r="C10" s="252" t="str">
+        <x:v>Refresh Cookie</x:v>
+      </x:c>
+      <x:c r="D10" s="252" t="str">
+        <x:v>有効・未失効Token</x:v>
+      </x:c>
+      <x:c r="E10" s="252" t="str">
+        <x:v>認証済/本人/共通条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="251" t="str">
+        <x:v>DS-AUTH-004</x:v>
+      </x:c>
+      <x:c r="B11" s="251" t="str">
+        <x:v>API-AUTH-004</x:v>
+      </x:c>
+      <x:c r="C11" s="251" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D11" s="251" t="str">
+        <x:v>本人</x:v>
+      </x:c>
+      <x:c r="E11" s="251" t="str">
+        <x:v>認証済/本人/共通条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" s="252" t="str">
+        <x:v>DS-AUTH-005</x:v>
+      </x:c>
+      <x:c r="B12" s="252" t="str">
+        <x:v>API-AUTH-005</x:v>
+      </x:c>
+      <x:c r="C12" s="252" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D12" s="252" t="str">
+        <x:v>本人</x:v>
+      </x:c>
+      <x:c r="E12" s="252" t="str">
+        <x:v>認証済/本人/共通条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="87" customHeight="1">
+      <x:c r="A13" s="251" t="str">
+        <x:v>DS-DASH-001</x:v>
+      </x:c>
+      <x:c r="B13" s="251" t="str">
+        <x:v>API-DASH-001</x:v>
+      </x:c>
+      <x:c r="C13" s="251" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D13" s="251" t="str">
+        <x:v>ADMIN=全社。PM=本人が現PMのPJまたは本人がACTIVE MemberのPJ。EMP=本人がACTIVE MemberのPJ。通知は本人のみ。</x:v>
+      </x:c>
+      <x:c r="E13" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="252" t="str">
+        <x:v>DS-DEPT-001</x:v>
+      </x:c>
+      <x:c r="B14" s="252" t="str">
+        <x:v>API-DEPT-001</x:v>
+      </x:c>
+      <x:c r="C14" s="252" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D14" s="252" t="str">
+        <x:v>一般=有効部門, 管理者=指定可</x:v>
+      </x:c>
+      <x:c r="E14" s="252" t="str">
+        <x:v>認証済/本人/共通条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="36" customHeight="1">
+      <x:c r="A15" s="251" t="str">
+        <x:v>DS-DEPT-002</x:v>
+      </x:c>
+      <x:c r="B15" s="251" t="str">
+        <x:v>API-DEPT-002</x:v>
+      </x:c>
+      <x:c r="C15" s="251" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D15" s="251" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E15" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" s="252" t="str">
+        <x:v>DS-DEPT-003</x:v>
+      </x:c>
+      <x:c r="B16" s="252" t="str">
+        <x:v>API-DEPT-003</x:v>
+      </x:c>
+      <x:c r="C16" s="252" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D16" s="252" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E16" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="251" t="str">
+        <x:v>DS-DEPT-004</x:v>
+      </x:c>
+      <x:c r="B17" s="251" t="str">
+        <x:v>API-DEPT-004</x:v>
+      </x:c>
+      <x:c r="C17" s="251" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D17" s="251" t="str">
+        <x:v>自己・子孫を親に設定不可</x:v>
+      </x:c>
+      <x:c r="E17" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="252" t="str">
+        <x:v>DS-DEPT-005</x:v>
+      </x:c>
+      <x:c r="B18" s="252" t="str">
+        <x:v>API-DEPT-005</x:v>
+      </x:c>
+      <x:c r="C18" s="252" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D18" s="252" t="str">
+        <x:v>Root以外かつ社員履歴・子部門なし</x:v>
+      </x:c>
+      <x:c r="E18" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="87" customHeight="1">
+      <x:c r="A19" s="251" t="str">
+        <x:v>DS-EMP-001</x:v>
+      </x:c>
+      <x:c r="B19" s="251" t="str">
+        <x:v>API-EMP-001</x:v>
+      </x:c>
+      <x:c r="C19" s="251" t="str">
+        <x:v>管理者/PM</x:v>
+      </x:c>
+      <x:c r="D19" s="251" t="str">
+        <x:v>ADMIN=全社。PM=本人が現PMのPLANNING/IN_PROGRESS/SUSPENDED PJのACTIVE MemberかつEMPLOYED社員（本人を含む）。</x:v>
+      </x:c>
+      <x:c r="E19" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="87" customHeight="1">
+      <x:c r="A20" s="252" t="str">
+        <x:v>DS-EMP-002</x:v>
+      </x:c>
+      <x:c r="B20" s="252" t="str">
+        <x:v>API-EMP-002</x:v>
+      </x:c>
+      <x:c r="C20" s="252" t="str">
+        <x:v>管理者/PM</x:v>
+      </x:c>
+      <x:c r="D20" s="252" t="str">
+        <x:v>ADMIN=全社員・全PJ/Task履歴。PM=担当未完了PJのACTIVE Memberかつ在籍社員、その社員の当該担当未完了PJ/Taskのみ</x:v>
+      </x:c>
+      <x:c r="E20" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="36" customHeight="1">
+      <x:c r="A21" s="251" t="str">
+        <x:v>DS-EMP-003</x:v>
+      </x:c>
+      <x:c r="B21" s="251" t="str">
+        <x:v>API-EMP-003</x:v>
+      </x:c>
+      <x:c r="C21" s="251" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D21" s="251" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E21" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="36" customHeight="1">
+      <x:c r="A22" s="252" t="str">
+        <x:v>DS-EMP-004</x:v>
+      </x:c>
+      <x:c r="B22" s="252" t="str">
+        <x:v>API-EMP-004</x:v>
+      </x:c>
+      <x:c r="C22" s="252" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D22" s="252" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E22" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="36" customHeight="1">
+      <x:c r="A23" s="251" t="str">
+        <x:v>DS-EMP-005</x:v>
+      </x:c>
+      <x:c r="B23" s="251" t="str">
+        <x:v>API-EMP-005</x:v>
+      </x:c>
+      <x:c r="C23" s="251" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D23" s="251" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E23" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="72" customHeight="1">
+      <x:c r="A24" s="252" t="str">
+        <x:v>DS-EMP-006</x:v>
+      </x:c>
+      <x:c r="B24" s="252" t="str">
+        <x:v>API-EMP-006</x:v>
+      </x:c>
+      <x:c r="C24" s="252" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D24" s="252" t="str">
+        <x:v>管理者のみ; 行単位検証・行単位Transaction。成功行のみCommit、失敗行Rollback。部分成功可</x:v>
+      </x:c>
+      <x:c r="E24" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="36" customHeight="1">
+      <x:c r="A25" s="251" t="str">
+        <x:v>DS-EMP-007</x:v>
+      </x:c>
+      <x:c r="B25" s="251" t="str">
+        <x:v>API-EMP-007</x:v>
+      </x:c>
+      <x:c r="C25" s="251" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D25" s="251" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E25" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="36" customHeight="1">
+      <x:c r="A26" s="252" t="str">
+        <x:v>DS-LOG-001</x:v>
+      </x:c>
+      <x:c r="B26" s="252" t="str">
+        <x:v>API-LOG-001</x:v>
+      </x:c>
+      <x:c r="C26" s="252" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D26" s="252" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E26" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="36" customHeight="1">
+      <x:c r="A27" s="251" t="str">
+        <x:v>DS-LOG-002</x:v>
+      </x:c>
+      <x:c r="B27" s="251" t="str">
+        <x:v>API-LOG-002</x:v>
+      </x:c>
+      <x:c r="C27" s="251" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D27" s="251" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E27" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="36" customHeight="1">
+      <x:c r="A28" s="252" t="str">
+        <x:v>DS-MST-001</x:v>
+      </x:c>
+      <x:c r="B28" s="252" t="str">
+        <x:v>API-MST-001</x:v>
+      </x:c>
+      <x:c r="C28" s="252" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D28" s="252" t="str">
+        <x:v>有効部門</x:v>
+      </x:c>
+      <x:c r="E28" s="252" t="str">
+        <x:v>認証済/本人/共通条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="222" customHeight="1">
+      <x:c r="A29" s="251" t="str">
+        <x:v>DS-MST-002</x:v>
+      </x:c>
+      <x:c r="B29" s="251" t="str">
+        <x:v>API-MST-002</x:v>
+      </x:c>
+      <x:c r="C29" s="251" t="str">
+        <x:v>管理者/PM</x:v>
+      </x:c>
+      <x:c r="D29" s="251" t="str">
+        <x:v>DEFAULTは既存社員参照範囲。PROJECT_PM/PROJECT_MEMBERはADMINまたはprojectIdの現PMかつ対応PJ/Member書込Permission必須（ADMIN新規PJ時だけprojectId省略可）。全社の在籍/有効UserからPMはROLE-PM保有者、MemberはACTIVE重複なし・直近離脱日&lt;当日の社員を候補にする。PMも同日再参加不可。社員詳細の閲覧範囲は拡張しない。</x:v>
+      </x:c>
+      <x:c r="E29" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="36" customHeight="1">
+      <x:c r="A30" s="252" t="str">
+        <x:v>DS-MST-003</x:v>
+      </x:c>
+      <x:c r="B30" s="252" t="str">
+        <x:v>API-MST-003</x:v>
+      </x:c>
+      <x:c r="C30" s="252" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D30" s="252" t="str">
+        <x:v>権限範囲内PJ</x:v>
+      </x:c>
+      <x:c r="E30" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="36" customHeight="1">
+      <x:c r="A31" s="251" t="str">
+        <x:v>DS-MST-004</x:v>
+      </x:c>
+      <x:c r="B31" s="251" t="str">
+        <x:v>API-MST-004</x:v>
+      </x:c>
+      <x:c r="C31" s="251" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D31" s="251" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E31" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="36" customHeight="1">
+      <x:c r="A32" s="252" t="str">
+        <x:v>DS-NTF-001</x:v>
+      </x:c>
+      <x:c r="B32" s="252" t="str">
+        <x:v>API-NTF-001</x:v>
+      </x:c>
+      <x:c r="C32" s="252" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D32" s="252" t="str">
+        <x:v>本人通知のみ</x:v>
+      </x:c>
+      <x:c r="E32" s="252" t="str">
+        <x:v>認証済/本人/共通条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="36" customHeight="1">
+      <x:c r="A33" s="251" t="str">
+        <x:v>DS-NTF-002</x:v>
+      </x:c>
+      <x:c r="B33" s="251" t="str">
+        <x:v>API-NTF-002</x:v>
+      </x:c>
+      <x:c r="C33" s="251" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D33" s="251" t="str">
+        <x:v>本人通知のみ</x:v>
+      </x:c>
+      <x:c r="E33" s="251" t="str">
+        <x:v>認証済/本人/共通条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="36" customHeight="1">
+      <x:c r="A34" s="252" t="str">
+        <x:v>DS-NTF-003</x:v>
+      </x:c>
+      <x:c r="B34" s="252" t="str">
+        <x:v>API-NTF-003</x:v>
+      </x:c>
+      <x:c r="C34" s="252" t="str">
+        <x:v>本人</x:v>
+      </x:c>
+      <x:c r="D34" s="252" t="str">
+        <x:v>受信者本人</x:v>
+      </x:c>
+      <x:c r="E34" s="252" t="str">
+        <x:v>認証済/本人/共通条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="36" customHeight="1">
+      <x:c r="A35" s="251" t="str">
+        <x:v>DS-NTF-004</x:v>
+      </x:c>
+      <x:c r="B35" s="251" t="str">
+        <x:v>API-NTF-004</x:v>
+      </x:c>
+      <x:c r="C35" s="251" t="str">
+        <x:v>本人</x:v>
+      </x:c>
+      <x:c r="D35" s="251" t="str">
+        <x:v>受信者本人</x:v>
+      </x:c>
+      <x:c r="E35" s="251" t="str">
+        <x:v>認証済/本人/共通条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="42" customHeight="1">
+      <x:c r="A36" s="252" t="str">
+        <x:v>DS-PRJ-001</x:v>
+      </x:c>
+      <x:c r="B36" s="252" t="str">
+        <x:v>API-PRJ-001</x:v>
+      </x:c>
+      <x:c r="C36" s="252" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D36" s="252" t="str">
+        <x:v>ADMIN=全社, PM/EMP=担当・参加PJ</x:v>
+      </x:c>
+      <x:c r="E36" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="36" customHeight="1">
+      <x:c r="A37" s="251" t="str">
+        <x:v>DS-PRJ-002</x:v>
+      </x:c>
+      <x:c r="B37" s="251" t="str">
+        <x:v>API-PRJ-002</x:v>
+      </x:c>
+      <x:c r="C37" s="251" t="str">
+        <x:v>関係者</x:v>
+      </x:c>
+      <x:c r="D37" s="251" t="str">
+        <x:v>ADMINまたはPJ Member</x:v>
+      </x:c>
+      <x:c r="E37" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="36" customHeight="1">
+      <x:c r="A38" s="252" t="str">
+        <x:v>DS-PRJ-003</x:v>
+      </x:c>
+      <x:c r="B38" s="252" t="str">
+        <x:v>API-PRJ-003</x:v>
+      </x:c>
+      <x:c r="C38" s="252" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D38" s="252" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E38" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="36" customHeight="1">
+      <x:c r="A39" s="251" t="str">
+        <x:v>DS-PRJ-004</x:v>
+      </x:c>
+      <x:c r="B39" s="251" t="str">
+        <x:v>API-PRJ-004</x:v>
+      </x:c>
+      <x:c r="C39" s="251" t="str">
+        <x:v>管理者/担当PM</x:v>
+      </x:c>
+      <x:c r="D39" s="251" t="str">
+        <x:v>ADMINまたは当該PJのPM</x:v>
+      </x:c>
+      <x:c r="E39" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="57" customHeight="1">
+      <x:c r="A40" s="252" t="str">
+        <x:v>DS-PRJ-005</x:v>
+      </x:c>
+      <x:c r="B40" s="252" t="str">
+        <x:v>API-PRJ-005</x:v>
+      </x:c>
+      <x:c r="C40" s="252" t="str">
+        <x:v>管理者/担当PM</x:v>
+      </x:c>
+      <x:c r="D40" s="252" t="str">
+        <x:v>ADMINまたは現PM。合法PJ遷移、完了/取消は未完了Taskなし（16／27）。</x:v>
+      </x:c>
+      <x:c r="E40" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="36" customHeight="1">
+      <x:c r="A41" s="251" t="str">
+        <x:v>DS-PRJ-006</x:v>
+      </x:c>
+      <x:c r="B41" s="251" t="str">
+        <x:v>API-PRJ-006</x:v>
+      </x:c>
+      <x:c r="C41" s="251" t="str">
+        <x:v>関係者</x:v>
+      </x:c>
+      <x:c r="D41" s="251" t="str">
+        <x:v>ADMINまたはPJ Member</x:v>
+      </x:c>
+      <x:c r="E41" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="42" customHeight="1">
+      <x:c r="A42" s="252" t="str">
+        <x:v>DS-PRJ-007</x:v>
+      </x:c>
+      <x:c r="B42" s="252" t="str">
+        <x:v>API-PRJ-007</x:v>
+      </x:c>
+      <x:c r="C42" s="252" t="str">
+        <x:v>管理者/担当PM</x:v>
+      </x:c>
+      <x:c r="D42" s="252" t="str">
+        <x:v>ADMINまたは当該PJのPM; 在籍社員</x:v>
+      </x:c>
+      <x:c r="E42" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="42" customHeight="1">
+      <x:c r="A43" s="251" t="str">
+        <x:v>DS-PRJ-008</x:v>
+      </x:c>
+      <x:c r="B43" s="251" t="str">
+        <x:v>API-PRJ-008</x:v>
+      </x:c>
+      <x:c r="C43" s="251" t="str">
+        <x:v>管理者/担当PM</x:v>
+      </x:c>
+      <x:c r="D43" s="251" t="str">
+        <x:v>PM・未完了Task担当者は削除不可</x:v>
+      </x:c>
+      <x:c r="E43" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="36" customHeight="1">
+      <x:c r="A44" s="252" t="str">
+        <x:v>DS-ROLE-001</x:v>
+      </x:c>
+      <x:c r="B44" s="252" t="str">
+        <x:v>API-ROLE-001</x:v>
+      </x:c>
+      <x:c r="C44" s="252" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D44" s="252" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E44" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="36" customHeight="1">
+      <x:c r="A45" s="251" t="str">
+        <x:v>DS-ROLE-002</x:v>
+      </x:c>
+      <x:c r="B45" s="251" t="str">
+        <x:v>API-ROLE-002</x:v>
+      </x:c>
+      <x:c r="C45" s="251" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D45" s="251" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E45" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="36" customHeight="1">
+      <x:c r="A46" s="252" t="str">
+        <x:v>DS-ROLE-003</x:v>
+      </x:c>
+      <x:c r="B46" s="252" t="str">
+        <x:v>API-ROLE-003</x:v>
+      </x:c>
+      <x:c r="C46" s="252" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D46" s="252" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E46" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="72" customHeight="1">
+      <x:c r="A47" s="251" t="str">
+        <x:v>DS-ROLE-004</x:v>
+      </x:c>
+      <x:c r="B47" s="251" t="str">
+        <x:v>API-ROLE-004</x:v>
+      </x:c>
+      <x:c r="C47" s="251" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D47" s="251" t="str">
+        <x:v>ADMIN。全Role Code変更不可。組込Roleは名称/説明のみ、権限変更不可。</x:v>
+      </x:c>
+      <x:c r="E47" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="72" customHeight="1">
+      <x:c r="A48" s="252" t="str">
+        <x:v>DS-ROLE-005</x:v>
+      </x:c>
+      <x:c r="B48" s="252" t="str">
+        <x:v>API-ROLE-005</x:v>
+      </x:c>
+      <x:c r="C48" s="252" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D48" s="252" t="str">
+        <x:v>ADMIN。組込Role状態変更不可。カスタムRole停止は割当User0件（停止Userを含む）。</x:v>
+      </x:c>
+      <x:c r="E48" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="42" customHeight="1">
+      <x:c r="A49" s="251" t="str">
+        <x:v>DS-RPT-001</x:v>
+      </x:c>
+      <x:c r="B49" s="251" t="str">
+        <x:v>API-RPT-001</x:v>
+      </x:c>
+      <x:c r="C49" s="251" t="str">
+        <x:v>権限別</x:v>
+      </x:c>
+      <x:c r="D49" s="251" t="str">
+        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人</x:v>
+      </x:c>
+      <x:c r="E49" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="42" customHeight="1">
+      <x:c r="A50" s="252" t="str">
+        <x:v>DS-RPT-002</x:v>
+      </x:c>
+      <x:c r="B50" s="252" t="str">
+        <x:v>API-RPT-002</x:v>
+      </x:c>
+      <x:c r="C50" s="252" t="str">
+        <x:v>権限別</x:v>
+      </x:c>
+      <x:c r="D50" s="252" t="str">
+        <x:v>ADMIN=全社, PM=担当PJ, EMP=本人</x:v>
+      </x:c>
+      <x:c r="E50" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="72" customHeight="1">
+      <x:c r="A51" s="251" t="str">
+        <x:v>DS-RPT-003</x:v>
+      </x:c>
+      <x:c r="B51" s="251" t="str">
+        <x:v>API-RPT-003</x:v>
+      </x:c>
+      <x:c r="C51" s="251" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D51" s="251" t="str">
+        <x:v>登録対象は本人。報告日当日の参加履歴・在籍/PJ期間を確認（16／28）。</x:v>
+      </x:c>
+      <x:c r="E51" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="42" customHeight="1">
+      <x:c r="A52" s="252" t="str">
+        <x:v>DS-RPT-004</x:v>
+      </x:c>
+      <x:c r="B52" s="252" t="str">
+        <x:v>API-RPT-004</x:v>
+      </x:c>
+      <x:c r="C52" s="252" t="str">
+        <x:v>本人/管理者</x:v>
+      </x:c>
+      <x:c r="D52" s="252" t="str">
+        <x:v>本人=当日・前営業日, ADMIN=全期間</x:v>
+      </x:c>
+      <x:c r="E52" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="42" customHeight="1">
+      <x:c r="A53" s="251" t="str">
+        <x:v>DS-RPT-005</x:v>
+      </x:c>
+      <x:c r="B53" s="251" t="str">
+        <x:v>API-RPT-005</x:v>
+      </x:c>
+      <x:c r="C53" s="251" t="str">
+        <x:v>本人/管理者</x:v>
+      </x:c>
+      <x:c r="D53" s="251" t="str">
+        <x:v>本人=当日・前営業日, ADMIN=全期間</x:v>
+      </x:c>
+      <x:c r="E53" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="36" customHeight="1">
+      <x:c r="A54" s="252" t="str">
+        <x:v>DS-RPT-006</x:v>
+      </x:c>
+      <x:c r="B54" s="252" t="str">
+        <x:v>API-RPT-006</x:v>
+      </x:c>
+      <x:c r="C54" s="252" t="str">
+        <x:v>管理者/担当PM</x:v>
+      </x:c>
+      <x:c r="D54" s="252" t="str">
+        <x:v>ADMIN=全社, PM=担当PJ</x:v>
+      </x:c>
+      <x:c r="E54" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="42" customHeight="1">
+      <x:c r="A55" s="251" t="str">
+        <x:v>DS-TASK-001</x:v>
+      </x:c>
+      <x:c r="B55" s="251" t="str">
+        <x:v>API-TASK-001</x:v>
+      </x:c>
+      <x:c r="C55" s="251" t="str">
+        <x:v>全員</x:v>
+      </x:c>
+      <x:c r="D55" s="251" t="str">
+        <x:v>ADMIN=全社, PM=担当PJ, EMP=参加PJ・本人Task</x:v>
+      </x:c>
+      <x:c r="E55" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="36" customHeight="1">
+      <x:c r="A56" s="252" t="str">
+        <x:v>DS-TASK-002</x:v>
+      </x:c>
+      <x:c r="B56" s="252" t="str">
+        <x:v>API-TASK-002</x:v>
+      </x:c>
+      <x:c r="C56" s="252" t="str">
+        <x:v>関係者</x:v>
+      </x:c>
+      <x:c r="D56" s="252" t="str">
+        <x:v>ADMINまたはPJ Member</x:v>
+      </x:c>
+      <x:c r="E56" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="36" customHeight="1">
+      <x:c r="A57" s="251" t="str">
+        <x:v>DS-TASK-003</x:v>
+      </x:c>
+      <x:c r="B57" s="251" t="str">
+        <x:v>API-TASK-003</x:v>
+      </x:c>
+      <x:c r="C57" s="251" t="str">
+        <x:v>管理者/担当PM</x:v>
+      </x:c>
+      <x:c r="D57" s="251" t="str">
+        <x:v>ADMINまたは当該PJのPM</x:v>
+      </x:c>
+      <x:c r="E57" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="36" customHeight="1">
+      <x:c r="A58" s="252" t="str">
+        <x:v>DS-TASK-004</x:v>
+      </x:c>
+      <x:c r="B58" s="252" t="str">
+        <x:v>API-TASK-004</x:v>
+      </x:c>
+      <x:c r="C58" s="252" t="str">
+        <x:v>管理者/担当PM</x:v>
+      </x:c>
+      <x:c r="D58" s="252" t="str">
+        <x:v>ADMINまたは当該PJのPM</x:v>
+      </x:c>
+      <x:c r="E58" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="147" customHeight="1">
+      <x:c r="A59" s="251" t="str">
+        <x:v>DS-TASK-005</x:v>
+      </x:c>
+      <x:c r="B59" s="251" t="str">
+        <x:v>API-TASK-005</x:v>
+      </x:c>
+      <x:c r="C59" s="251" t="str">
+        <x:v>権限別</x:v>
+      </x:c>
+      <x:c r="D59" s="251" t="str">
+        <x:v>担当者=TODO/進行/REVIEW; PM/ADMIN=承認・差戻し・取消</x:v>
+      </x:c>
+      <x:c r="E59" s="251" t="str">
+        <x:v>着手・未着手へ戻す・確認依頼：PERM-TASK-PROGRESS、かつ担当者/担当PM/ADMIN。承認・差戻し：PERM-TASK-APPROVE、かつ担当PM/ADMIN。取消：PERM-TASK-WRITE、かつ担当PM/ADMIN。16／27の合法遷移も満たすこと。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="42" customHeight="1">
+      <x:c r="A60" s="252" t="str">
+        <x:v>DS-TASK-006</x:v>
+      </x:c>
+      <x:c r="B60" s="252" t="str">
+        <x:v>API-TASK-006</x:v>
+      </x:c>
+      <x:c r="C60" s="252" t="str">
+        <x:v>担当者/PM/管理者</x:v>
+      </x:c>
+      <x:c r="D60" s="252" t="str">
+        <x:v>担当者または担当PM/ADMIN</x:v>
+      </x:c>
+      <x:c r="E60" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="36" customHeight="1">
+      <x:c r="A61" s="251" t="str">
+        <x:v>DS-TASK-007</x:v>
+      </x:c>
+      <x:c r="B61" s="251" t="str">
+        <x:v>API-TASK-007</x:v>
+      </x:c>
+      <x:c r="C61" s="251" t="str">
+        <x:v>PJ Member</x:v>
+      </x:c>
+      <x:c r="D61" s="251" t="str">
+        <x:v>当該PJ Member</x:v>
+      </x:c>
+      <x:c r="E61" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="36" customHeight="1">
+      <x:c r="A62" s="252" t="str">
+        <x:v>DS-TASK-008</x:v>
+      </x:c>
+      <x:c r="B62" s="252" t="str">
+        <x:v>API-TASK-008</x:v>
+      </x:c>
+      <x:c r="C62" s="252" t="str">
+        <x:v>関係者</x:v>
+      </x:c>
+      <x:c r="D62" s="252" t="str">
+        <x:v>ADMINまたはPJ Member</x:v>
+      </x:c>
+      <x:c r="E62" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="36" customHeight="1">
+      <x:c r="A63" s="251" t="str">
+        <x:v>DS-TASK-009</x:v>
+      </x:c>
+      <x:c r="B63" s="251" t="str">
+        <x:v>API-TASK-009</x:v>
+      </x:c>
+      <x:c r="C63" s="251" t="str">
+        <x:v>関係者</x:v>
+      </x:c>
+      <x:c r="D63" s="251" t="str">
+        <x:v>ADMIN/PM/PJ Member</x:v>
+      </x:c>
+      <x:c r="E63" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="36" customHeight="1">
+      <x:c r="A64" s="252" t="str">
+        <x:v>DS-TASK-010</x:v>
+      </x:c>
+      <x:c r="B64" s="252" t="str">
+        <x:v>API-TASK-010</x:v>
+      </x:c>
+      <x:c r="C64" s="252" t="str">
+        <x:v>関係者</x:v>
+      </x:c>
+      <x:c r="D64" s="252" t="str">
+        <x:v>ADMIN/PM/PJ Member</x:v>
+      </x:c>
+      <x:c r="E64" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="36" customHeight="1">
+      <x:c r="A65" s="251" t="str">
+        <x:v>DS-TASK-011</x:v>
+      </x:c>
+      <x:c r="B65" s="251" t="str">
+        <x:v>API-TASK-011</x:v>
+      </x:c>
+      <x:c r="C65" s="251" t="str">
+        <x:v>権限者</x:v>
+      </x:c>
+      <x:c r="D65" s="251" t="str">
+        <x:v>ADMIN/担当PM/Upload者</x:v>
+      </x:c>
+      <x:c r="E65" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="36" customHeight="1">
+      <x:c r="A66" s="252" t="str">
+        <x:v>DS-USR-001</x:v>
+      </x:c>
+      <x:c r="B66" s="252" t="str">
+        <x:v>API-USR-001</x:v>
+      </x:c>
+      <x:c r="C66" s="252" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D66" s="252" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E66" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="36" customHeight="1">
+      <x:c r="A67" s="251" t="str">
+        <x:v>DS-USR-002</x:v>
+      </x:c>
+      <x:c r="B67" s="251" t="str">
+        <x:v>API-USR-002</x:v>
+      </x:c>
+      <x:c r="C67" s="251" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D67" s="251" t="str">
+        <x:v>管理者のみ</x:v>
+      </x:c>
+      <x:c r="E67" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="42" customHeight="1">
+      <x:c r="A68" s="252" t="str">
+        <x:v>DS-USR-003</x:v>
+      </x:c>
+      <x:c r="B68" s="252" t="str">
+        <x:v>API-USR-003</x:v>
+      </x:c>
+      <x:c r="C68" s="252" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D68" s="252" t="str">
+        <x:v>管理者のみ; 自身のADMIN剥奪禁止</x:v>
+      </x:c>
+      <x:c r="E68" s="252" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="36" customHeight="1">
+      <x:c r="A69" s="251" t="str">
+        <x:v>DS-USR-004</x:v>
+      </x:c>
+      <x:c r="B69" s="251" t="str">
+        <x:v>API-USR-004</x:v>
+      </x:c>
+      <x:c r="C69" s="251" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D69" s="251" t="str">
+        <x:v>管理者のみ; 有効User</x:v>
+      </x:c>
+      <x:c r="E69" s="251" t="str">
+        <x:v>Permission + Data範囲</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A3:E3"/>
+    <x:mergeCell ref="A5:E5"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/基本設計/02_権限基本設計書.xlsx
+++ b/基本設計/02_権限基本設計書.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R51d1f6bed6674a93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rb903e54b68224279"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_ロール定義" sheetId="10" r:id="Rd120777407f94afc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_メニュー権限" sheetId="11" r:id="R704dfdf16c73452a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_機能権限" sheetId="12" r:id="Rc5d3d8f041de4ce0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_権限コード" sheetId="13" r:id="R5072afd4190048ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_API権限対応" sheetId="14" r:id="R58d5e3ab94234d99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_DataScope定義" sheetId="15" r:id="R6d6d49eeaeb9461f"/>
-  </x:sheets>
-</x:workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheets>
+    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="Red7a016096414262"/>
+    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R22a2339b2a494254"/>
+    <ns0:sheet name="09_ロール定義" sheetId="10" ns1:id="R8a31b0ab31dd4e69"/>
+    <ns0:sheet name="10_メニュー権限" sheetId="11" ns1:id="R127af4c83c3e4088"/>
+    <ns0:sheet name="11_機能権限" sheetId="12" ns1:id="R6fba5db5a05e43ed"/>
+    <ns0:sheet name="12_権限コード" sheetId="13" ns1:id="R4f48ac6dba5a4439"/>
+    <ns0:sheet name="13_API権限対応" sheetId="14" ns1:id="R2812ea5abce04dd9"/>
+    <ns0:sheet name="14_DataScope定義" sheetId="15" ns1:id="R73c5b748e74d4ce8"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="27">
+  <x:fonts count="28">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -173,8 +173,13 @@
       <x:color rgb="FF193C61"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF17212B"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="31">
+  <x:fills count="34">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -326,6 +331,21 @@
         <x:fgColor rgb="FFF1F5FA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF3F8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="9">
     <x:border/>
@@ -403,7 +423,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="254">
+  <x:cellXfs count="264">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -940,6 +960,26 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1387,7 +1427,7 @@
       <x:c r="A11"/>
       <x:c r="B11"/>
       <x:c r="C11" s="235" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1424,7 +1464,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="238" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="E13" s="191"/>
       <x:c r="F13" s="191"/>
@@ -1442,7 +1482,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="238" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="E14" s="191"/>
       <x:c r="F14" s="191"/>
@@ -1478,7 +1518,7 @@
         <x:v>状態</x:v>
       </x:c>
       <x:c r="D16" s="238" t="str">
-        <x:v>Review中</x:v>
+        <x:v>修正済</x:v>
       </x:c>
       <x:c r="E16" s="191"/>
       <x:c r="F16" s="191"/>
@@ -1639,7 +1679,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="244" t="str">
-        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.6    改訂日：2026-09-29    Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="63"/>
       <x:c r="C4" s="63"/>
@@ -2115,6 +2155,32 @@
       </x:c>
       <x:c r="H21" s="240" t="str">
         <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="95" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>CHG-MENU-20260929-01：U-01対応。固定Menu Code・menus契約・下流Bindingを整合。既存権限・Route・DBは変更なし。</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>方式合意に基づく補完。成果物の正式承認は別途。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2199,7 +2265,7 @@
       </x:c>
       <x:c r="B4" s="23"/>
       <x:c r="C4" s="242" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="23" t="str">
@@ -2207,7 +2273,7 @@
       </x:c>
       <x:c r="F4" s="23"/>
       <x:c r="G4" s="243" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="H4"/>
       <x:c r="I4"/>
@@ -2562,11 +2628,11 @@
       </x:c>
       <x:c r="B4" s="23"/>
       <x:c r="C4" s="242" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="241" t="str">
-        <x:v>作成日：2026-09-24</x:v>
+        <x:v>作成日：2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="35"/>
       <x:c r="G4" s="36"/>
@@ -2980,6 +3046,466 @@
       </x:c>
       <x:c r="F22" s="33" t="str"/>
     </x:row>
+    <x:row r="25" ht="30" customHeight="1">
+      <x:c r="A25" s="255" t="str">
+        <x:v>2. Menu Code定義（API-AUTH-004 menus正本）</x:v>
+      </x:c>
+      <x:c r="B25" s="255"/>
+      <x:c r="C25" s="255"/>
+      <x:c r="D25" s="255"/>
+      <x:c r="E25" s="255"/>
+      <x:c r="F25" s="255"/>
+    </x:row>
+    <x:row r="26" ht="30" customHeight="1">
+      <x:c r="A26" s="263" t="str">
+        <x:v>Menu Code</x:v>
+      </x:c>
+      <x:c r="B26" s="263" t="str">
+        <x:v>表示名（上表参照）</x:v>
+      </x:c>
+      <x:c r="C26" s="263" t="str">
+        <x:v>画面ID</x:v>
+      </x:c>
+      <x:c r="D26" s="263" t="str">
+        <x:v>表示順</x:v>
+      </x:c>
+      <x:c r="E26" s="263" t="str">
+        <x:v>固定Query</x:v>
+      </x:c>
+      <x:c r="F26" s="263" t="str">
+        <x:v>権限参照</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="42" customHeight="1">
+      <x:c r="A27" s="259" t="str">
+        <x:v>MENU-HOME</x:v>
+      </x:c>
+      <x:c r="B27" s="259" t="str">
+        <x:v>ダッシュボード</x:v>
+      </x:c>
+      <x:c r="C27" s="259" t="str">
+        <x:v>SCR-002</x:v>
+      </x:c>
+      <x:c r="D27" s="259" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F27" s="259" t="str">
+        <x:v>本Sheet行8のRole条件。認証済共通。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="262" t="str">
+        <x:v>MENU-EMPLOYEES</x:v>
+      </x:c>
+      <x:c r="B28" s="262" t="str">
+        <x:v>従業員管理</x:v>
+      </x:c>
+      <x:c r="C28" s="262" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="D28" s="262" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E28" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F28" s="262" t="str">
+        <x:v>本Sheet行9のRole条件。PERM-EMP-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="42" customHeight="1">
+      <x:c r="A29" s="259" t="str">
+        <x:v>MENU-DEPARTMENTS</x:v>
+      </x:c>
+      <x:c r="B29" s="259" t="str">
+        <x:v>部門管理</x:v>
+      </x:c>
+      <x:c r="C29" s="259" t="str">
+        <x:v>SCR-007</x:v>
+      </x:c>
+      <x:c r="D29" s="259" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E29" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F29" s="259" t="str">
+        <x:v>本Sheet行10のRole条件。PERM-DEPT-WRITE（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="262" t="str">
+        <x:v>MENU-PROJECTS</x:v>
+      </x:c>
+      <x:c r="B30" s="262" t="str">
+        <x:v>プロジェクト一覧</x:v>
+      </x:c>
+      <x:c r="C30" s="262" t="str">
+        <x:v>SCR-008</x:v>
+      </x:c>
+      <x:c r="D30" s="262" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E30" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F30" s="262" t="str">
+        <x:v>本Sheet行11のRole条件。PERM-PRJ-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="42" customHeight="1">
+      <x:c r="A31" s="259" t="str">
+        <x:v>MENU-MY-PROJECTS</x:v>
+      </x:c>
+      <x:c r="B31" s="259" t="str">
+        <x:v>マイプロジェクト</x:v>
+      </x:c>
+      <x:c r="C31" s="259" t="str">
+        <x:v>SCR-008</x:v>
+      </x:c>
+      <x:c r="D31" s="259" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E31" s="259" t="str">
+        <x:v>mine=true</x:v>
+      </x:c>
+      <x:c r="F31" s="259" t="str">
+        <x:v>本Sheet行12のRole条件。PERM-PRJ-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="42" customHeight="1">
+      <x:c r="A32" s="262" t="str">
+        <x:v>MENU-TASKS</x:v>
+      </x:c>
+      <x:c r="B32" s="262" t="str">
+        <x:v>全タスク</x:v>
+      </x:c>
+      <x:c r="C32" s="262" t="str">
+        <x:v>SCR-013</x:v>
+      </x:c>
+      <x:c r="D32" s="262" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E32" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F32" s="262" t="str">
+        <x:v>本Sheet行13のRole条件。PERM-TASK-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="42" customHeight="1">
+      <x:c r="A33" s="259" t="str">
+        <x:v>MENU-MY-TASKS</x:v>
+      </x:c>
+      <x:c r="B33" s="259" t="str">
+        <x:v>マイタスク</x:v>
+      </x:c>
+      <x:c r="C33" s="259" t="str">
+        <x:v>SCR-014</x:v>
+      </x:c>
+      <x:c r="D33" s="259" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E33" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F33" s="259" t="str">
+        <x:v>本Sheet行14のRole条件。PERM-TASK-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="A34" s="262" t="str">
+        <x:v>MENU-TASK-BOARD</x:v>
+      </x:c>
+      <x:c r="B34" s="262" t="str">
+        <x:v>タスクボード</x:v>
+      </x:c>
+      <x:c r="C34" s="262" t="str">
+        <x:v>SCR-018</x:v>
+      </x:c>
+      <x:c r="D34" s="262" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E34" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F34" s="262" t="str">
+        <x:v>本Sheet行15のRole条件。PERM-TASK-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="42" customHeight="1">
+      <x:c r="A35" s="259" t="str">
+        <x:v>MENU-MY-REPORTS</x:v>
+      </x:c>
+      <x:c r="B35" s="259" t="str">
+        <x:v>マイ日報</x:v>
+      </x:c>
+      <x:c r="C35" s="259" t="str">
+        <x:v>SCR-019</x:v>
+      </x:c>
+      <x:c r="D35" s="259" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E35" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F35" s="259" t="str">
+        <x:v>本Sheet行16のRole条件。PERM-RPT-SELF（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="42" customHeight="1">
+      <x:c r="A36" s="262" t="str">
+        <x:v>MENU-REPORT-SEARCH</x:v>
+      </x:c>
+      <x:c r="B36" s="262" t="str">
+        <x:v>日報検索</x:v>
+      </x:c>
+      <x:c r="C36" s="262" t="str">
+        <x:v>SCR-021</x:v>
+      </x:c>
+      <x:c r="D36" s="262" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E36" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F36" s="262" t="str">
+        <x:v>本Sheet行17のRole条件。PERM-RPT-TEAM（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
+      <x:c r="A37" s="259" t="str">
+        <x:v>MENU-NOTIFICATIONS</x:v>
+      </x:c>
+      <x:c r="B37" s="259" t="str">
+        <x:v>通知一覧</x:v>
+      </x:c>
+      <x:c r="C37" s="259" t="str">
+        <x:v>SCR-022</x:v>
+      </x:c>
+      <x:c r="D37" s="259" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E37" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F37" s="259" t="str">
+        <x:v>本Sheet行19のRole条件。認証済共通。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="42" customHeight="1">
+      <x:c r="A38" s="262" t="str">
+        <x:v>MENU-USERS</x:v>
+      </x:c>
+      <x:c r="B38" s="262" t="str">
+        <x:v>ユーザー管理</x:v>
+      </x:c>
+      <x:c r="C38" s="262" t="str">
+        <x:v>SCR-023</x:v>
+      </x:c>
+      <x:c r="D38" s="262" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E38" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F38" s="262" t="str">
+        <x:v>本Sheet行20のRole条件。PERM-USER-ADMIN（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="42" customHeight="1">
+      <x:c r="A39" s="259" t="str">
+        <x:v>MENU-ROLES</x:v>
+      </x:c>
+      <x:c r="B39" s="259" t="str">
+        <x:v>ロール/権限</x:v>
+      </x:c>
+      <x:c r="C39" s="259" t="str">
+        <x:v>SCR-024</x:v>
+      </x:c>
+      <x:c r="D39" s="259" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E39" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F39" s="259" t="str">
+        <x:v>本Sheet行21のRole条件。PERM-ROLE-ADMIN（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="42" customHeight="1">
+      <x:c r="A40" s="262" t="str">
+        <x:v>MENU-LOGS</x:v>
+      </x:c>
+      <x:c r="B40" s="262" t="str">
+        <x:v>操作ログ</x:v>
+      </x:c>
+      <x:c r="C40" s="262" t="str">
+        <x:v>SCR-025</x:v>
+      </x:c>
+      <x:c r="D40" s="262" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E40" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F40" s="262" t="str">
+        <x:v>本Sheet行22のRole条件。PERM-LOG-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="30" customHeight="1">
+      <x:c r="A44" s="255" t="str">
+        <x:v>3. Menu生成・利用規則</x:v>
+      </x:c>
+      <x:c r="B44" s="255"/>
+      <x:c r="C44" s="255"/>
+      <x:c r="D44" s="255"/>
+      <x:c r="E44" s="255"/>
+      <x:c r="F44" s="255"/>
+    </x:row>
+    <x:row r="45" ht="30" customHeight="1">
+      <x:c r="A45" s="263" t="str">
+        <x:v>項目</x:v>
+      </x:c>
+      <x:c r="B45" s="263" t="str">
+        <x:v>定義</x:v>
+      </x:c>
+      <x:c r="C45" s="263" t="str">
+        <x:v>参照</x:v>
+      </x:c>
+      <x:c r="D45" s="263" t="str">
+        <x:v>対象</x:v>
+      </x:c>
+      <x:c r="E45" s="263" t="str">
+        <x:v>条件</x:v>
+      </x:c>
+      <x:c r="F45" s="263" t="str">
+        <x:v>補足</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="57" customHeight="1">
+      <x:c r="A46" s="259" t="str">
+        <x:v>識別値</x:v>
+      </x:c>
+      <x:c r="B46" s="259" t="str">
+        <x:v>Menu Codeは表示名ではなく固定識別子。大文字小文字を区別し、部分一致・Trim変換をしない。</x:v>
+      </x:c>
+      <x:c r="C46" s="259" t="str">
+        <x:v>本Sheet2節</x:v>
+      </x:c>
+      <x:c r="D46" s="259" t="str">
+        <x:v>API-AUTH-004</x:v>
+      </x:c>
+      <x:c r="E46" s="259" t="str">
+        <x:v>第1期14 Menu</x:v>
+      </x:c>
+      <x:c r="F46" s="259" t="str">
+        <x:v>親見出しは返却しない。日報統計（行18）は第1期非提供のためCodeを追加・返却しない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="57" customHeight="1">
+      <x:c r="A47" s="262" t="str">
+        <x:v>表示候補</x:v>
+      </x:c>
+      <x:c r="B47" s="262" t="str">
+        <x:v>有効Roleの上表許可を和集合にし、必要Permissionと積集合。表示順の昇順で重複なしのCode配列を返す。</x:v>
+      </x:c>
+      <x:c r="C47" s="262" t="str">
+        <x:v>09・12／本Sheet1・2節</x:v>
+      </x:c>
+      <x:c r="D47" s="262" t="str">
+        <x:v>roles / permissions / menus</x:v>
+      </x:c>
+      <x:c r="E47" s="262" t="str">
+        <x:v>未許可Menuは返さない</x:v>
+      </x:c>
+      <x:c r="F47" s="262" t="str">
+        <x:v>Role・Data Scopeを拡張しない。Homeは共通安全画面。Dashboard集計APIのPERM-DASH-READは別判定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="57" customHeight="1">
+      <x:c r="A48" s="259" t="str">
+        <x:v>空配列</x:v>
+      </x:c>
+      <x:c r="B48" s="259" t="str">
+        <x:v>menus=[]は許容する。ClientはMenuを自動補完せず、空の親見出しも表示しない。</x:v>
+      </x:c>
+      <x:c r="C48" s="259" t="str">
+        <x:v>10／23_API項目定義</x:v>
+      </x:c>
+      <x:c r="D48" s="259" t="str">
+        <x:v>Menu表示</x:v>
+      </x:c>
+      <x:c r="E48" s="259" t="str">
+        <x:v>Null・Null要素不可</x:v>
+      </x:c>
+      <x:c r="F48" s="259" t="str">
+        <x:v>通常の組込Role利用者は上表により表示候補を持つ。空配列の許容は権限拡張を意味しない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="42" customHeight="1">
+      <x:c r="A49" s="262" t="str">
+        <x:v>画面遷移</x:v>
+      </x:c>
+      <x:c r="B49" s="262" t="str">
+        <x:v>画面IDのPathは03のRoute定義を参照。固定Queryは2節による。</x:v>
+      </x:c>
+      <x:c r="C49" s="262" t="str">
+        <x:v>03／20_画面Route定義</x:v>
+      </x:c>
+      <x:c r="D49" s="262" t="str">
+        <x:v>各Menu選択</x:v>
+      </x:c>
+      <x:c r="E49" s="262" t="str">
+        <x:v>遷移前にGuardを実行</x:v>
+      </x:c>
+      <x:c r="F49" s="262" t="str">
+        <x:v>マイプロジェクトはSCR-008にmine=trueを付ける。親見出しにリンクを設定しない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="57" customHeight="1">
+      <x:c r="A50" s="259" t="str">
+        <x:v>Client防御</x:v>
+      </x:c>
+      <x:c r="B50" s="259" t="str">
+        <x:v>未知の文字列Codeは無視しリンク化しない。重複Codeは表示時に1件へ集約する。</x:v>
+      </x:c>
+      <x:c r="C50" s="259" t="str">
+        <x:v>10／23_API項目定義</x:v>
+      </x:c>
+      <x:c r="D50" s="259" t="str">
+        <x:v>Menu構築</x:v>
+      </x:c>
+      <x:c r="E50" s="259" t="str">
+        <x:v>CodeをURL・HTMLとして使用しない</x:v>
+      </x:c>
+      <x:c r="F50" s="259" t="str">
+        <x:v>Serverは2節のCodeのみ・重複なしを保証。Clientの防御は契約外の値を正規Codeと認めるものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="42" customHeight="1">
+      <x:c r="A51" s="262" t="str">
+        <x:v>強制改密</x:v>
+      </x:c>
+      <x:c r="B51" s="262" t="str">
+        <x:v>passwordMustChange=trueの表示・遷移制限は既定Guardに従う。</x:v>
+      </x:c>
+      <x:c r="C51" s="262" t="str">
+        <x:v>03／20_画面Route定義</x:v>
+      </x:c>
+      <x:c r="D51" s="262" t="str">
+        <x:v>SCR-026</x:v>
+      </x:c>
+      <x:c r="E51" s="262" t="str">
+        <x:v>通常Menuを表示しない</x:v>
+      </x:c>
+      <x:c r="F51" s="262" t="str">
+        <x:v>menus生成で既存Role/Permissionを変更しない。画面・APIの最終認可はMenu表示とは別に実施する。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F2"/>
@@ -2991,6 +3517,8 @@
     <x:mergeCell ref="C4:D4"/>
     <x:mergeCell ref="A6:F6"/>
     <x:mergeCell ref="E4:G4"/>
+    <x:mergeCell ref="A25:F25"/>
+    <x:mergeCell ref="A44:F44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3067,7 +3595,7 @@
       </x:c>
       <x:c r="B4" s="23"/>
       <x:c r="C4" s="242" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="23" t="str">
@@ -3075,7 +3603,7 @@
       </x:c>
       <x:c r="F4" s="23"/>
       <x:c r="G4" s="243" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="H4"/>
       <x:c r="I4"/>
@@ -3708,13 +4236,13 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="62" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="E4" s="63"/>
       <x:c r="F4" s="63"/>
@@ -4281,14 +4809,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="141" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="139"/>
       <x:c r="G4" s="139"/>

--- a/基本設計/02_権限基本設計書.xlsx
+++ b/基本設計/02_権限基本設計書.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheets>
-    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="Red7a016096414262"/>
-    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R22a2339b2a494254"/>
-    <ns0:sheet name="09_ロール定義" sheetId="10" ns1:id="R8a31b0ab31dd4e69"/>
-    <ns0:sheet name="10_メニュー権限" sheetId="11" ns1:id="R127af4c83c3e4088"/>
-    <ns0:sheet name="11_機能権限" sheetId="12" ns1:id="R6fba5db5a05e43ed"/>
-    <ns0:sheet name="12_権限コード" sheetId="13" ns1:id="R4f48ac6dba5a4439"/>
-    <ns0:sheet name="13_API権限対応" sheetId="14" ns1:id="R2812ea5abce04dd9"/>
-    <ns0:sheet name="14_DataScope定義" sheetId="15" ns1:id="R73c5b748e74d4ce8"/>
-  </ns0:sheets>
-</ns0:workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R7728b4bf12e74352"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rac74ab5c151a400f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_ロール定義" sheetId="10" r:id="R6f6f1215829b4c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_メニュー権限" sheetId="11" r:id="Rb6f9b9e03ec04f18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_機能権限" sheetId="12" r:id="R4ba298b69da74d42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_権限コード" sheetId="13" r:id="Rb4dd9d762fb84365"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_API権限対応" sheetId="14" r:id="R7bec95dd6aab47c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_DataScope定義" sheetId="15" r:id="R068cbfe117d64e91"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2165,7 +2165,7 @@
         <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>CHG-MENU-20260929-01：U-01対応。固定Menu Code・menus契約・下流Bindingを整合。既存権限・Route・DBは変更なし。</x:v>
+        <x:v>CHG-MENU-20260929-01：U-01対応。固定Menu Code・menus契約・下流Bindingを整合。既存権限・Route・DBは変更なし。 Menu Code正本化を確認。Menu欄のData Scope本文を正本参照へ統一。</x:v>
       </x:c>
       <x:c r="D22" t="str">
         <x:v>－</x:v>
@@ -2741,7 +2741,7 @@
         <x:v>×</x:v>
       </x:c>
       <x:c r="F9" s="33" t="str">
-        <x:v>PMは担当する未完了PJのACTIVE Memberかつ在籍社員のみ参照。更新系Menu/操作は非表示</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。更新系Menu／操作は非表示。</x:v>
       </x:c>
       <x:c r="G9"/>
       <x:c r="H9"/>
@@ -2791,7 +2791,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="F11" s="33" t="str">
-        <x:v>担当・参加範囲</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。</x:v>
       </x:c>
       <x:c r="G11"/>
       <x:c r="H11"/>
@@ -2843,7 +2843,7 @@
         <x:v>×</x:v>
       </x:c>
       <x:c r="F13" s="33" t="str">
-        <x:v>PMは担当PJ</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。</x:v>
       </x:c>
       <x:c r="G13"/>
       <x:c r="H13"/>
@@ -2893,7 +2893,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="F15" s="33" t="str">
-        <x:v>参加PJのみ</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。</x:v>
       </x:c>
       <x:c r="G15"/>
       <x:c r="H15"/>
@@ -2943,7 +2943,7 @@
         <x:v>×</x:v>
       </x:c>
       <x:c r="F17" s="33" t="str">
-        <x:v>PMは担当PJ</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="40" customHeight="1">
@@ -2989,7 +2989,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="F19" s="33" t="str">
-        <x:v>本人通知</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">

--- a/基本設計/02_権限基本設計書.xlsx
+++ b/基本設計/02_権限基本設計書.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R51d1f6bed6674a93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rb903e54b68224279"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_ロール定義" sheetId="10" r:id="Rd120777407f94afc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_メニュー権限" sheetId="11" r:id="R704dfdf16c73452a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_機能権限" sheetId="12" r:id="Rc5d3d8f041de4ce0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_権限コード" sheetId="13" r:id="R5072afd4190048ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_API権限対応" sheetId="14" r:id="R58d5e3ab94234d99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_DataScope定義" sheetId="15" r:id="R6d6d49eeaeb9461f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R7728b4bf12e74352"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rac74ab5c151a400f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_ロール定義" sheetId="10" r:id="R6f6f1215829b4c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_メニュー権限" sheetId="11" r:id="Rb6f9b9e03ec04f18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_機能権限" sheetId="12" r:id="R4ba298b69da74d42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_権限コード" sheetId="13" r:id="Rb4dd9d762fb84365"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_API権限対応" sheetId="14" r:id="R7bec95dd6aab47c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_DataScope定義" sheetId="15" r:id="R068cbfe117d64e91"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="27">
+  <x:fonts count="28">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -173,8 +173,13 @@
       <x:color rgb="FF193C61"/>
       <x:name val="Yu Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF17212B"/>
+      <x:name val="Yu Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="31">
+  <x:fills count="34">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -326,6 +331,21 @@
         <x:fgColor rgb="FFF1F5FA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF3F8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="9">
     <x:border/>
@@ -403,7 +423,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="254">
+  <x:cellXfs count="264">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -940,6 +960,26 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="27" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1387,7 +1427,7 @@
       <x:c r="A11"/>
       <x:c r="B11"/>
       <x:c r="C11" s="235" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D11"/>
       <x:c r="E11"/>
@@ -1424,7 +1464,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="D13" s="238" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="E13" s="191"/>
       <x:c r="F13" s="191"/>
@@ -1442,7 +1482,7 @@
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D14" s="238" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="E14" s="191"/>
       <x:c r="F14" s="191"/>
@@ -1478,7 +1518,7 @@
         <x:v>状態</x:v>
       </x:c>
       <x:c r="D16" s="238" t="str">
-        <x:v>Review中</x:v>
+        <x:v>修正済</x:v>
       </x:c>
       <x:c r="E16" s="191"/>
       <x:c r="F16" s="191"/>
@@ -1639,7 +1679,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="244" t="str">
-        <x:v>版数：Ver.2.5    改訂日：2026-09-24    Baseline：BL-2026-09-24</x:v>
+        <x:v>版数：Ver.2.6    改訂日：2026-09-29    Baseline：BL-2026-09-24</x:v>
       </x:c>
       <x:c r="B4" s="63"/>
       <x:c r="C4" s="63"/>
@@ -2115,6 +2155,32 @@
       </x:c>
       <x:c r="H21" s="240" t="str">
         <x:v>BL-2026-09-24。責任者・Review者・承認者はProject Leaderが記入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="95" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>Ver.2.6</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>2026-09-29</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>CHG-MENU-20260929-01：U-01対応。固定Menu Code・menus契約・下流Bindingを整合。既存権限・Route・DBは変更なし。 Menu Code正本化を確認。Menu欄のData Scope本文を正本参照へ統一。</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>修正済</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>方式合意に基づく補完。成果物の正式承認は別途。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2199,7 +2265,7 @@
       </x:c>
       <x:c r="B4" s="23"/>
       <x:c r="C4" s="242" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="23" t="str">
@@ -2207,7 +2273,7 @@
       </x:c>
       <x:c r="F4" s="23"/>
       <x:c r="G4" s="243" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="H4"/>
       <x:c r="I4"/>
@@ -2562,11 +2628,11 @@
       </x:c>
       <x:c r="B4" s="23"/>
       <x:c r="C4" s="242" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="241" t="str">
-        <x:v>作成日：2026-09-24</x:v>
+        <x:v>作成日：2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="35"/>
       <x:c r="G4" s="36"/>
@@ -2675,7 +2741,7 @@
         <x:v>×</x:v>
       </x:c>
       <x:c r="F9" s="33" t="str">
-        <x:v>PMは担当する未完了PJのACTIVE Memberかつ在籍社員のみ参照。更新系Menu/操作は非表示</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。更新系Menu／操作は非表示。</x:v>
       </x:c>
       <x:c r="G9"/>
       <x:c r="H9"/>
@@ -2725,7 +2791,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="F11" s="33" t="str">
-        <x:v>担当・参加範囲</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。</x:v>
       </x:c>
       <x:c r="G11"/>
       <x:c r="H11"/>
@@ -2777,7 +2843,7 @@
         <x:v>×</x:v>
       </x:c>
       <x:c r="F13" s="33" t="str">
-        <x:v>PMは担当PJ</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。</x:v>
       </x:c>
       <x:c r="G13"/>
       <x:c r="H13"/>
@@ -2827,7 +2893,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="F15" s="33" t="str">
-        <x:v>参加PJのみ</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。</x:v>
       </x:c>
       <x:c r="G15"/>
       <x:c r="H15"/>
@@ -2877,7 +2943,7 @@
         <x:v>×</x:v>
       </x:c>
       <x:c r="F17" s="33" t="str">
-        <x:v>PMは担当PJ</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="40" customHeight="1">
@@ -2923,7 +2989,7 @@
         <x:v>○</x:v>
       </x:c>
       <x:c r="F19" s="33" t="str">
-        <x:v>本人通知</x:v>
+        <x:v>Data Scopeは本書14_DataScope定義、API対応は13_API権限対応を参照。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2979,6 +3045,466 @@
         <x:v>×</x:v>
       </x:c>
       <x:c r="F22" s="33" t="str"/>
+    </x:row>
+    <x:row r="25" ht="30" customHeight="1">
+      <x:c r="A25" s="255" t="str">
+        <x:v>2. Menu Code定義（API-AUTH-004 menus正本）</x:v>
+      </x:c>
+      <x:c r="B25" s="255"/>
+      <x:c r="C25" s="255"/>
+      <x:c r="D25" s="255"/>
+      <x:c r="E25" s="255"/>
+      <x:c r="F25" s="255"/>
+    </x:row>
+    <x:row r="26" ht="30" customHeight="1">
+      <x:c r="A26" s="263" t="str">
+        <x:v>Menu Code</x:v>
+      </x:c>
+      <x:c r="B26" s="263" t="str">
+        <x:v>表示名（上表参照）</x:v>
+      </x:c>
+      <x:c r="C26" s="263" t="str">
+        <x:v>画面ID</x:v>
+      </x:c>
+      <x:c r="D26" s="263" t="str">
+        <x:v>表示順</x:v>
+      </x:c>
+      <x:c r="E26" s="263" t="str">
+        <x:v>固定Query</x:v>
+      </x:c>
+      <x:c r="F26" s="263" t="str">
+        <x:v>権限参照</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="42" customHeight="1">
+      <x:c r="A27" s="259" t="str">
+        <x:v>MENU-HOME</x:v>
+      </x:c>
+      <x:c r="B27" s="259" t="str">
+        <x:v>ダッシュボード</x:v>
+      </x:c>
+      <x:c r="C27" s="259" t="str">
+        <x:v>SCR-002</x:v>
+      </x:c>
+      <x:c r="D27" s="259" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E27" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F27" s="259" t="str">
+        <x:v>本Sheet行8のRole条件。認証済共通。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="262" t="str">
+        <x:v>MENU-EMPLOYEES</x:v>
+      </x:c>
+      <x:c r="B28" s="262" t="str">
+        <x:v>従業員管理</x:v>
+      </x:c>
+      <x:c r="C28" s="262" t="str">
+        <x:v>SCR-003</x:v>
+      </x:c>
+      <x:c r="D28" s="262" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E28" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F28" s="262" t="str">
+        <x:v>本Sheet行9のRole条件。PERM-EMP-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="42" customHeight="1">
+      <x:c r="A29" s="259" t="str">
+        <x:v>MENU-DEPARTMENTS</x:v>
+      </x:c>
+      <x:c r="B29" s="259" t="str">
+        <x:v>部門管理</x:v>
+      </x:c>
+      <x:c r="C29" s="259" t="str">
+        <x:v>SCR-007</x:v>
+      </x:c>
+      <x:c r="D29" s="259" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E29" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F29" s="259" t="str">
+        <x:v>本Sheet行10のRole条件。PERM-DEPT-WRITE（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="262" t="str">
+        <x:v>MENU-PROJECTS</x:v>
+      </x:c>
+      <x:c r="B30" s="262" t="str">
+        <x:v>プロジェクト一覧</x:v>
+      </x:c>
+      <x:c r="C30" s="262" t="str">
+        <x:v>SCR-008</x:v>
+      </x:c>
+      <x:c r="D30" s="262" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E30" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F30" s="262" t="str">
+        <x:v>本Sheet行11のRole条件。PERM-PRJ-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="42" customHeight="1">
+      <x:c r="A31" s="259" t="str">
+        <x:v>MENU-MY-PROJECTS</x:v>
+      </x:c>
+      <x:c r="B31" s="259" t="str">
+        <x:v>マイプロジェクト</x:v>
+      </x:c>
+      <x:c r="C31" s="259" t="str">
+        <x:v>SCR-008</x:v>
+      </x:c>
+      <x:c r="D31" s="259" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E31" s="259" t="str">
+        <x:v>mine=true</x:v>
+      </x:c>
+      <x:c r="F31" s="259" t="str">
+        <x:v>本Sheet行12のRole条件。PERM-PRJ-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="42" customHeight="1">
+      <x:c r="A32" s="262" t="str">
+        <x:v>MENU-TASKS</x:v>
+      </x:c>
+      <x:c r="B32" s="262" t="str">
+        <x:v>全タスク</x:v>
+      </x:c>
+      <x:c r="C32" s="262" t="str">
+        <x:v>SCR-013</x:v>
+      </x:c>
+      <x:c r="D32" s="262" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E32" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F32" s="262" t="str">
+        <x:v>本Sheet行13のRole条件。PERM-TASK-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="42" customHeight="1">
+      <x:c r="A33" s="259" t="str">
+        <x:v>MENU-MY-TASKS</x:v>
+      </x:c>
+      <x:c r="B33" s="259" t="str">
+        <x:v>マイタスク</x:v>
+      </x:c>
+      <x:c r="C33" s="259" t="str">
+        <x:v>SCR-014</x:v>
+      </x:c>
+      <x:c r="D33" s="259" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E33" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F33" s="259" t="str">
+        <x:v>本Sheet行14のRole条件。PERM-TASK-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="A34" s="262" t="str">
+        <x:v>MENU-TASK-BOARD</x:v>
+      </x:c>
+      <x:c r="B34" s="262" t="str">
+        <x:v>タスクボード</x:v>
+      </x:c>
+      <x:c r="C34" s="262" t="str">
+        <x:v>SCR-018</x:v>
+      </x:c>
+      <x:c r="D34" s="262" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E34" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F34" s="262" t="str">
+        <x:v>本Sheet行15のRole条件。PERM-TASK-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="42" customHeight="1">
+      <x:c r="A35" s="259" t="str">
+        <x:v>MENU-MY-REPORTS</x:v>
+      </x:c>
+      <x:c r="B35" s="259" t="str">
+        <x:v>マイ日報</x:v>
+      </x:c>
+      <x:c r="C35" s="259" t="str">
+        <x:v>SCR-019</x:v>
+      </x:c>
+      <x:c r="D35" s="259" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E35" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F35" s="259" t="str">
+        <x:v>本Sheet行16のRole条件。PERM-RPT-SELF（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="42" customHeight="1">
+      <x:c r="A36" s="262" t="str">
+        <x:v>MENU-REPORT-SEARCH</x:v>
+      </x:c>
+      <x:c r="B36" s="262" t="str">
+        <x:v>日報検索</x:v>
+      </x:c>
+      <x:c r="C36" s="262" t="str">
+        <x:v>SCR-021</x:v>
+      </x:c>
+      <x:c r="D36" s="262" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E36" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F36" s="262" t="str">
+        <x:v>本Sheet行17のRole条件。PERM-RPT-TEAM（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
+      <x:c r="A37" s="259" t="str">
+        <x:v>MENU-NOTIFICATIONS</x:v>
+      </x:c>
+      <x:c r="B37" s="259" t="str">
+        <x:v>通知一覧</x:v>
+      </x:c>
+      <x:c r="C37" s="259" t="str">
+        <x:v>SCR-022</x:v>
+      </x:c>
+      <x:c r="D37" s="259" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E37" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F37" s="259" t="str">
+        <x:v>本Sheet行19のRole条件。認証済共通。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="42" customHeight="1">
+      <x:c r="A38" s="262" t="str">
+        <x:v>MENU-USERS</x:v>
+      </x:c>
+      <x:c r="B38" s="262" t="str">
+        <x:v>ユーザー管理</x:v>
+      </x:c>
+      <x:c r="C38" s="262" t="str">
+        <x:v>SCR-023</x:v>
+      </x:c>
+      <x:c r="D38" s="262" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E38" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F38" s="262" t="str">
+        <x:v>本Sheet行20のRole条件。PERM-USER-ADMIN（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="42" customHeight="1">
+      <x:c r="A39" s="259" t="str">
+        <x:v>MENU-ROLES</x:v>
+      </x:c>
+      <x:c r="B39" s="259" t="str">
+        <x:v>ロール/権限</x:v>
+      </x:c>
+      <x:c r="C39" s="259" t="str">
+        <x:v>SCR-024</x:v>
+      </x:c>
+      <x:c r="D39" s="259" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E39" s="259" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F39" s="259" t="str">
+        <x:v>本Sheet行21のRole条件。PERM-ROLE-ADMIN（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="42" customHeight="1">
+      <x:c r="A40" s="262" t="str">
+        <x:v>MENU-LOGS</x:v>
+      </x:c>
+      <x:c r="B40" s="262" t="str">
+        <x:v>操作ログ</x:v>
+      </x:c>
+      <x:c r="C40" s="262" t="str">
+        <x:v>SCR-025</x:v>
+      </x:c>
+      <x:c r="D40" s="262" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E40" s="262" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="F40" s="262" t="str">
+        <x:v>本Sheet行22のRole条件。PERM-LOG-READ（12参照）。Data Scopeは13・14参照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="30" customHeight="1">
+      <x:c r="A44" s="255" t="str">
+        <x:v>3. Menu生成・利用規則</x:v>
+      </x:c>
+      <x:c r="B44" s="255"/>
+      <x:c r="C44" s="255"/>
+      <x:c r="D44" s="255"/>
+      <x:c r="E44" s="255"/>
+      <x:c r="F44" s="255"/>
+    </x:row>
+    <x:row r="45" ht="30" customHeight="1">
+      <x:c r="A45" s="263" t="str">
+        <x:v>項目</x:v>
+      </x:c>
+      <x:c r="B45" s="263" t="str">
+        <x:v>定義</x:v>
+      </x:c>
+      <x:c r="C45" s="263" t="str">
+        <x:v>参照</x:v>
+      </x:c>
+      <x:c r="D45" s="263" t="str">
+        <x:v>対象</x:v>
+      </x:c>
+      <x:c r="E45" s="263" t="str">
+        <x:v>条件</x:v>
+      </x:c>
+      <x:c r="F45" s="263" t="str">
+        <x:v>補足</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="57" customHeight="1">
+      <x:c r="A46" s="259" t="str">
+        <x:v>識別値</x:v>
+      </x:c>
+      <x:c r="B46" s="259" t="str">
+        <x:v>Menu Codeは表示名ではなく固定識別子。大文字小文字を区別し、部分一致・Trim変換をしない。</x:v>
+      </x:c>
+      <x:c r="C46" s="259" t="str">
+        <x:v>本Sheet2節</x:v>
+      </x:c>
+      <x:c r="D46" s="259" t="str">
+        <x:v>API-AUTH-004</x:v>
+      </x:c>
+      <x:c r="E46" s="259" t="str">
+        <x:v>第1期14 Menu</x:v>
+      </x:c>
+      <x:c r="F46" s="259" t="str">
+        <x:v>親見出しは返却しない。日報統計（行18）は第1期非提供のためCodeを追加・返却しない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="57" customHeight="1">
+      <x:c r="A47" s="262" t="str">
+        <x:v>表示候補</x:v>
+      </x:c>
+      <x:c r="B47" s="262" t="str">
+        <x:v>有効Roleの上表許可を和集合にし、必要Permissionと積集合。表示順の昇順で重複なしのCode配列を返す。</x:v>
+      </x:c>
+      <x:c r="C47" s="262" t="str">
+        <x:v>09・12／本Sheet1・2節</x:v>
+      </x:c>
+      <x:c r="D47" s="262" t="str">
+        <x:v>roles / permissions / menus</x:v>
+      </x:c>
+      <x:c r="E47" s="262" t="str">
+        <x:v>未許可Menuは返さない</x:v>
+      </x:c>
+      <x:c r="F47" s="262" t="str">
+        <x:v>Role・Data Scopeを拡張しない。Homeは共通安全画面。Dashboard集計APIのPERM-DASH-READは別判定。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="57" customHeight="1">
+      <x:c r="A48" s="259" t="str">
+        <x:v>空配列</x:v>
+      </x:c>
+      <x:c r="B48" s="259" t="str">
+        <x:v>menus=[]は許容する。ClientはMenuを自動補完せず、空の親見出しも表示しない。</x:v>
+      </x:c>
+      <x:c r="C48" s="259" t="str">
+        <x:v>10／23_API項目定義</x:v>
+      </x:c>
+      <x:c r="D48" s="259" t="str">
+        <x:v>Menu表示</x:v>
+      </x:c>
+      <x:c r="E48" s="259" t="str">
+        <x:v>Null・Null要素不可</x:v>
+      </x:c>
+      <x:c r="F48" s="259" t="str">
+        <x:v>通常の組込Role利用者は上表により表示候補を持つ。空配列の許容は権限拡張を意味しない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="42" customHeight="1">
+      <x:c r="A49" s="262" t="str">
+        <x:v>画面遷移</x:v>
+      </x:c>
+      <x:c r="B49" s="262" t="str">
+        <x:v>画面IDのPathは03のRoute定義を参照。固定Queryは2節による。</x:v>
+      </x:c>
+      <x:c r="C49" s="262" t="str">
+        <x:v>03／20_画面Route定義</x:v>
+      </x:c>
+      <x:c r="D49" s="262" t="str">
+        <x:v>各Menu選択</x:v>
+      </x:c>
+      <x:c r="E49" s="262" t="str">
+        <x:v>遷移前にGuardを実行</x:v>
+      </x:c>
+      <x:c r="F49" s="262" t="str">
+        <x:v>マイプロジェクトはSCR-008にmine=trueを付ける。親見出しにリンクを設定しない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="57" customHeight="1">
+      <x:c r="A50" s="259" t="str">
+        <x:v>Client防御</x:v>
+      </x:c>
+      <x:c r="B50" s="259" t="str">
+        <x:v>未知の文字列Codeは無視しリンク化しない。重複Codeは表示時に1件へ集約する。</x:v>
+      </x:c>
+      <x:c r="C50" s="259" t="str">
+        <x:v>10／23_API項目定義</x:v>
+      </x:c>
+      <x:c r="D50" s="259" t="str">
+        <x:v>Menu構築</x:v>
+      </x:c>
+      <x:c r="E50" s="259" t="str">
+        <x:v>CodeをURL・HTMLとして使用しない</x:v>
+      </x:c>
+      <x:c r="F50" s="259" t="str">
+        <x:v>Serverは2節のCodeのみ・重複なしを保証。Clientの防御は契約外の値を正規Codeと認めるものではない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="42" customHeight="1">
+      <x:c r="A51" s="262" t="str">
+        <x:v>強制改密</x:v>
+      </x:c>
+      <x:c r="B51" s="262" t="str">
+        <x:v>passwordMustChange=trueの表示・遷移制限は既定Guardに従う。</x:v>
+      </x:c>
+      <x:c r="C51" s="262" t="str">
+        <x:v>03／20_画面Route定義</x:v>
+      </x:c>
+      <x:c r="D51" s="262" t="str">
+        <x:v>SCR-026</x:v>
+      </x:c>
+      <x:c r="E51" s="262" t="str">
+        <x:v>通常Menuを表示しない</x:v>
+      </x:c>
+      <x:c r="F51" s="262" t="str">
+        <x:v>menus生成で既存Role/Permissionを変更しない。画面・APIの最終認可はMenu表示とは別に実施する。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2991,6 +3517,8 @@
     <x:mergeCell ref="C4:D4"/>
     <x:mergeCell ref="A6:F6"/>
     <x:mergeCell ref="E4:G4"/>
+    <x:mergeCell ref="A25:F25"/>
+    <x:mergeCell ref="A44:F44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3067,7 +3595,7 @@
       </x:c>
       <x:c r="B4" s="23"/>
       <x:c r="C4" s="242" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="D4" s="21"/>
       <x:c r="E4" s="23" t="str">
@@ -3075,7 +3603,7 @@
       </x:c>
       <x:c r="F4" s="23"/>
       <x:c r="G4" s="243" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="H4"/>
       <x:c r="I4"/>
@@ -3708,13 +4236,13 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="62" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="D4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="E4" s="63"/>
       <x:c r="F4" s="63"/>
@@ -4281,14 +4809,14 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B4" s="63" t="str">
-        <x:v>Ver.2.5</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="C4" s="139"/>
       <x:c r="D4" s="141" t="str">
         <x:v>改訂日</x:v>
       </x:c>
       <x:c r="E4" s="63" t="str">
-        <x:v>2026-09-24</x:v>
+        <x:v>2026-09-29</x:v>
       </x:c>
       <x:c r="F4" s="139"/>
       <x:c r="G4" s="139"/>
